--- a/others/customize.governance/instances/dashboards/dashboard_v1.xlsx
+++ b/others/customize.governance/instances/dashboards/dashboard_v1.xlsx
@@ -1496,7 +1496,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>402133.0</v>
+        <v>402132.0</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1510,102 +1510,23 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Templates</t>
+          <t>ISMS Introduction</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>This dashboard provides a list of pre-loaded policy templates to inspire your company's policies.</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>/recordm/index.html#/cob.custom-resource/402133/dash</t>
+          <t>/recordm/index.html#/cob.custom-resource/402132/dash</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
-        <is>
-          <t>{ 
-"mycolab": list("Colaborador", "username:{{user.username}}", 1, 0),
-"my_politics": list("Politica v2", "template:no {{vars.politicaSearch}}", 100, 0, "nome","true"),
-}</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>h-full bg-cover bg-center text-black overflow-auto p-3 !bg-none !bg-sky-50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Classes, Image, Access, Context</t>
-        </is>
-      </c>
-      <c r="K18"/>
-      <c r="L18"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>/recordm/recordm/instances/180/files/108/it-security.jpg</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Gestão da solução Governance</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>fa-building-shield</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>GOV</t>
-        </is>
-      </c>
-      <c r="R18"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>402132.0</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ISMS Introduction</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>/recordm/index.html#/cob.custom-resource/402132/dash</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
         <is>
           <t>{ 
 "mycolab": list("Colaborador", "username:{{user.username}}", 1, 0),
@@ -1616,44 +1537,44 @@
 }</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>h-full bg-cover bg-center text-black overflow-auto p-3 !bg-none !bg-sky-50</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Classes, Image, Access, Context</t>
         </is>
       </c>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19" t="inlineStr">
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>/recordm/recordm/instances/180/files/108/it-security.jpg</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Gestão da solução Governance</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>fa-building-shield</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>GOV</t>
         </is>
       </c>
-      <c r="R19"/>
+      <c r="R18"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2360,7 +2281,7 @@
         <v>402146.0</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C25" t="n">
         <v>1.0</v>
@@ -2386,7 +2307,7 @@
         <v>402146.0</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C26" t="n">
         <v>1.0</v>
@@ -2412,7 +2333,7 @@
         <v>402146.0</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C27" t="n">
         <v>1.0</v>
@@ -2438,7 +2359,7 @@
         <v>402146.0</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C28" t="n">
         <v>1.0</v>
@@ -2464,7 +2385,7 @@
         <v>402146.0</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C29" t="n">
         <v>1.0</v>
@@ -2490,7 +2411,7 @@
         <v>402146.0</v>
       </c>
       <c r="B30" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C30" t="n">
         <v>1.0</v>
@@ -2516,7 +2437,7 @@
         <v>402146.0</v>
       </c>
       <c r="B31" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C31" t="n">
         <v>1.0</v>
@@ -2542,7 +2463,7 @@
         <v>402146.0</v>
       </c>
       <c r="B32" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C32" t="n">
         <v>1.0</v>
@@ -2568,7 +2489,7 @@
         <v>402146.0</v>
       </c>
       <c r="B33" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C33" t="n">
         <v>1.0</v>
@@ -2594,7 +2515,7 @@
         <v>402146.0</v>
       </c>
       <c r="B34" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C34" t="n">
         <v>1.0</v>
@@ -2620,7 +2541,7 @@
         <v>402146.0</v>
       </c>
       <c r="B35" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C35" t="n">
         <v>3.0</v>
@@ -2646,7 +2567,7 @@
         <v>402146.0</v>
       </c>
       <c r="B36" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C36" t="n">
         <v>3.0</v>
@@ -2672,7 +2593,7 @@
         <v>402146.0</v>
       </c>
       <c r="B37" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C37" t="n">
         <v>1.0</v>
@@ -2698,7 +2619,7 @@
         <v>402146.0</v>
       </c>
       <c r="B38" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C38" t="n">
         <v>1.0</v>
@@ -2724,7 +2645,7 @@
         <v>402146.0</v>
       </c>
       <c r="B39" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C39" t="n">
         <v>1.0</v>
@@ -4958,7 +4879,7 @@
         <v>402146.0</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C25" t="n">
         <v>1.0</v>
@@ -4986,7 +4907,7 @@
         <v>402146.0</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C26" t="n">
         <v>1.0</v>
@@ -5014,7 +4935,7 @@
         <v>402146.0</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C27" t="n">
         <v>1.0</v>
@@ -5042,7 +4963,7 @@
         <v>402146.0</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C28" t="n">
         <v>1.0</v>
@@ -5070,7 +4991,7 @@
         <v>402146.0</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C29" t="n">
         <v>1.0</v>
@@ -5098,7 +5019,7 @@
         <v>402146.0</v>
       </c>
       <c r="B30" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C30" t="n">
         <v>1.0</v>
@@ -5126,7 +5047,7 @@
         <v>402146.0</v>
       </c>
       <c r="B31" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C31" t="n">
         <v>1.0</v>
@@ -5154,7 +5075,7 @@
         <v>402146.0</v>
       </c>
       <c r="B32" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C32" t="n">
         <v>1.0</v>
@@ -5182,7 +5103,7 @@
         <v>402146.0</v>
       </c>
       <c r="B33" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C33" t="n">
         <v>1.0</v>
@@ -5218,7 +5139,7 @@
         <v>402146.0</v>
       </c>
       <c r="B34" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C34" t="n">
         <v>1.0</v>
@@ -5254,7 +5175,7 @@
         <v>402146.0</v>
       </c>
       <c r="B35" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C35" t="n">
         <v>3.0</v>
@@ -5290,7 +5211,7 @@
         <v>402146.0</v>
       </c>
       <c r="B36" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C36" t="n">
         <v>3.0</v>
@@ -5326,7 +5247,7 @@
         <v>402146.0</v>
       </c>
       <c r="B37" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C37" t="n">
         <v>1.0</v>
@@ -5354,7 +5275,7 @@
         <v>402146.0</v>
       </c>
       <c r="B38" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C38" t="n">
         <v>1.0</v>
@@ -5382,7 +5303,7 @@
         <v>402146.0</v>
       </c>
       <c r="B39" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C39" t="n">
         <v>1.0</v>
@@ -7095,7 +7016,7 @@
   <cols>
     <col min="1" max="1" width="8.3046875" customWidth="true"/>
     <col min="2" max="2" width="18.28125" customWidth="true"/>
-    <col min="3" max="3" width="12.97265625" customWidth="true"/>
+    <col min="3" max="3" width="15.48046875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7130,20 +7051,20 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>402148.0</v>
+        <v>402149.0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>GOV Base ISO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>402147.0</v>
+        <v>402148.0</v>
       </c>
       <c r="B4" t="n">
         <v>0.0</v>
@@ -7156,20 +7077,20 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>402146.0</v>
+        <v>402148.0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>GOV Base ISO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>402145.0</v>
+        <v>402147.0</v>
       </c>
       <c r="B6" t="n">
         <v>0.0</v>
@@ -7182,20 +7103,20 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>402144.0</v>
+        <v>402147.0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>GOV Base ISO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>402143.0</v>
+        <v>402146.0</v>
       </c>
       <c r="B8" t="n">
         <v>0.0</v>
@@ -7208,20 +7129,20 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>402142.0</v>
+        <v>402146.0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>GOV Base ISO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>402141.0</v>
+        <v>402145.0</v>
       </c>
       <c r="B10" t="n">
         <v>0.0</v>
@@ -7234,20 +7155,20 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>402140.0</v>
+        <v>402145.0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>GOV Base ISO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>402139.0</v>
+        <v>402144.0</v>
       </c>
       <c r="B12" t="n">
         <v>0.0</v>
@@ -7260,20 +7181,20 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>402138.0</v>
+        <v>402144.0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>GOV Base ISO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>402137.0</v>
+        <v>402143.0</v>
       </c>
       <c r="B14" t="n">
         <v>0.0</v>
@@ -7286,20 +7207,20 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>402136.0</v>
+        <v>402143.0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>GOV Base ISO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>402135.0</v>
+        <v>402142.0</v>
       </c>
       <c r="B16" t="n">
         <v>0.0</v>
@@ -7312,20 +7233,20 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>402134.0</v>
+        <v>402142.0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>GOV Base ISO</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>402133.0</v>
+        <v>402141.0</v>
       </c>
       <c r="B18" t="n">
         <v>0.0</v>
@@ -7338,14 +7259,274 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>402141.0</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GOV Base ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>402140.0</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>402140.0</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GOV Base ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>402139.0</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>402139.0</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GOV Base ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>402138.0</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>402138.0</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GOV Base ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>402138.0</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GOV Base Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>402137.0</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>402137.0</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GOV Base ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>402136.0</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>402136.0</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>GOV Base ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>402136.0</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>GOV Base Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>402135.0</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>402135.0</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GOV Base ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>402135.0</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>GOV Base Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>402134.0</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>402134.0</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GOV Base ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>402134.0</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GOV Base Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>402132.0</v>
       </c>
-      <c r="B19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B38" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>402132.0</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GOV Base ISO</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7546,7 @@
     <col min="4" max="4" width="14.8359375" customWidth="true"/>
     <col min="8" max="8" width="27.05078125" customWidth="true"/>
     <col min="9" max="9" width="63.765625" customWidth="true"/>
-    <col min="11" max="11" width="12.30078125" customWidth="true"/>
+    <col min="11" max="11" width="11.03515625" customWidth="true"/>
     <col min="12" max="12" width="10.48046875" customWidth="true"/>
     <col min="16" max="16" width="50.61328125" customWidth="true"/>
     <col min="17" max="17" width="19.828125" customWidth="true"/>
@@ -7382,7 +7563,7 @@
     <col min="31" max="31" width="40.40625" customWidth="true"/>
     <col min="33" max="33" width="35.64453125" customWidth="true"/>
     <col min="34" max="34" width="10.546875" customWidth="true"/>
-    <col min="35" max="35" width="133.46484375" customWidth="true"/>
+    <col min="35" max="35" width="54.03125" customWidth="true"/>
     <col min="36" max="36" width="39.1015625" customWidth="true"/>
     <col min="37" max="37" width="7.94921875" customWidth="true"/>
     <col min="39" max="39" width="61.5234375" customWidth="true"/>
@@ -10221,7 +10402,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="E33"/>
@@ -10235,8 +10416,16 @@
       <c r="M33"/>
       <c r="N33"/>
       <c r="O33"/>
-      <c r="P33"/>
-      <c r="Q33"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>w-full max-w-xl resize-none min-h-min h-min border border-slate-300 rounded-md outline-slate-300 leading-5</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Classes, Placeholder</t>
+        </is>
+      </c>
       <c r="R33"/>
       <c r="S33"/>
       <c r="T33"/>
@@ -10247,11 +10436,7 @@
       <c r="Y33"/>
       <c r="Z33"/>
       <c r="AA33"/>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>Risks p/ Classification</t>
-        </is>
-      </c>
+      <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33"/>
       <c r="AE33"/>
@@ -10272,12 +10457,20 @@
       <c r="AT33"/>
       <c r="AU33"/>
       <c r="AV33"/>
-      <c r="AW33"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>myrisk</t>
+        </is>
+      </c>
       <c r="AX33"/>
       <c r="AY33"/>
       <c r="AZ33"/>
       <c r="BA33"/>
-      <c r="BB33"/>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>Search Risks...</t>
+        </is>
+      </c>
       <c r="BC33"/>
       <c r="BD33"/>
       <c r="BE33"/>
@@ -10292,14 +10485,14 @@
         <v>402146.0</v>
       </c>
       <c r="B34" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C34" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>List</t>
         </is>
       </c>
       <c r="E34"/>
@@ -10330,9 +10523,21 @@
       <c r="AD34"/>
       <c r="AE34"/>
       <c r="AF34"/>
-      <c r="AG34"/>
-      <c r="AH34"/>
-      <c r="AI34"/>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>ShowViews</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Work Item</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>-state:"Done" business_process_reference:*Risk Management*</t>
+        </is>
+      </c>
       <c r="AJ34"/>
       <c r="AK34"/>
       <c r="AL34"/>
@@ -10366,7 +10571,7 @@
         <v>402146.0</v>
       </c>
       <c r="B35" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="C35" t="n">
         <v>0.0</v>
@@ -10401,7 +10606,7 @@
       <c r="AA35"/>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Risks p/ Origin</t>
+          <t>Risks p/ Classification</t>
         </is>
       </c>
       <c r="AC35"/>
@@ -10444,7 +10649,7 @@
         <v>402146.0</v>
       </c>
       <c r="B36" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="C36" t="n">
         <v>1.0</v>
@@ -10518,7 +10723,7 @@
         <v>402146.0</v>
       </c>
       <c r="B37" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="C37" t="n">
         <v>0.0</v>
@@ -10553,7 +10758,7 @@
       <c r="AA37"/>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Risks Review</t>
+          <t>Risks p/ Origin</t>
         </is>
       </c>
       <c r="AC37"/>
@@ -10596,7 +10801,7 @@
         <v>402146.0</v>
       </c>
       <c r="B38" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="C38" t="n">
         <v>1.0</v>
@@ -10670,10 +10875,10 @@
         <v>402146.0</v>
       </c>
       <c r="B39" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C39" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -10705,7 +10910,7 @@
       <c r="AA39"/>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Risks Implemenation</t>
+          <t>Risks Review</t>
         </is>
       </c>
       <c r="AC39"/>
@@ -10748,10 +10953,10 @@
         <v>402146.0</v>
       </c>
       <c r="B40" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C40" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -10822,10 +11027,10 @@
         <v>402146.0</v>
       </c>
       <c r="B41" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -10857,7 +11062,7 @@
       <c r="AA41"/>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Risks p/ State</t>
+          <t>Risks Implemenation</t>
         </is>
       </c>
       <c r="AC41"/>
@@ -10900,10 +11105,10 @@
         <v>402146.0</v>
       </c>
       <c r="B42" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C42" t="n">
         <v>3.0</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1.0</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10974,10 +11179,10 @@
         <v>402146.0</v>
       </c>
       <c r="B43" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C43" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -11009,21 +11214,11 @@
       <c r="AA43"/>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>&lt;div class=""&gt;
-&lt;a href="/recordm/index.html#/instance/create/49" onclick="" class="text-white bg-green-700 hover:bg-green-800 focus:outline-none focus:ring-4 focus:ring-green-300 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 dark:bg-green-600 dark:hover:bg-green-700 dark:focus:ring-green-800 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-triangle-exclamation fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;Register Risk&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
-&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>text-center font-bold pt-4</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+          <t>Risks p/ State</t>
+        </is>
+      </c>
+      <c r="AC43"/>
+      <c r="AD43"/>
       <c r="AE43"/>
       <c r="AF43"/>
       <c r="AG43"/>
@@ -11062,14 +11257,14 @@
         <v>402146.0</v>
       </c>
       <c r="B44" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E44"/>
@@ -11083,16 +11278,8 @@
       <c r="M44"/>
       <c r="N44"/>
       <c r="O44"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>w-full max-w-xl resize-none min-h-min h-min border border-slate-300 rounded-md py-2 px-2 outline-slate-300 leading-5</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Classes, Placeholder</t>
-        </is>
-      </c>
+      <c r="P44"/>
+      <c r="Q44"/>
       <c r="R44"/>
       <c r="S44"/>
       <c r="T44"/>
@@ -11124,20 +11311,12 @@
       <c r="AT44"/>
       <c r="AU44"/>
       <c r="AV44"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>myrisk</t>
-        </is>
-      </c>
+      <c r="AW44"/>
       <c r="AX44"/>
       <c r="AY44"/>
       <c r="AZ44"/>
       <c r="BA44"/>
-      <c r="BB44" t="inlineStr">
-        <is>
-          <t>Search Risks...</t>
-        </is>
-      </c>
+      <c r="BB44"/>
       <c r="BC44"/>
       <c r="BD44"/>
       <c r="BE44"/>
@@ -11155,11 +11334,11 @@
         <v>5.0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E45"/>
@@ -11183,15 +11362,25 @@
       <c r="W45"/>
       <c r="X45"/>
       <c r="Y45"/>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>InputVar, Query</t>
-        </is>
-      </c>
+      <c r="Z45"/>
       <c r="AA45"/>
-      <c r="AB45"/>
-      <c r="AC45"/>
-      <c r="AD45"/>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>&lt;div class=""&gt;
+&lt;a href="/recordm/index.html#/instance/create/49" onclick="" class="text-white bg-green-700 hover:bg-green-800 focus:outline-none focus:ring-4 focus:ring-green-300 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 dark:bg-green-600 dark:hover:bg-green-700 dark:focus:ring-green-800 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-triangle-exclamation fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;Register Risk&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>text-center font-bold pt-4</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE45"/>
       <c r="AF45"/>
       <c r="AG45"/>
@@ -11218,11 +11407,7 @@
       <c r="BB45"/>
       <c r="BC45"/>
       <c r="BD45"/>
-      <c r="BE45" t="inlineStr">
-        <is>
-          <t>/kibana/s/governance/app/dashboards#/view/c6a08800-fe67-11ee-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
-        </is>
-      </c>
+      <c r="BE45"/>
       <c r="BF45"/>
       <c r="BG45"/>
       <c r="BH45"/>
@@ -11231,17 +11416,17 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>402145.0</v>
+        <v>402146.0</v>
       </c>
       <c r="B46" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="C46" t="n">
         <v>0.0</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="E46"/>
@@ -11265,13 +11450,13 @@
       <c r="W46"/>
       <c r="X46"/>
       <c r="Y46"/>
-      <c r="Z46"/>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>InputVar, Query</t>
+        </is>
+      </c>
       <c r="AA46"/>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>Vulnerabilities p/ State</t>
-        </is>
-      </c>
+      <c r="AB46"/>
       <c r="AC46"/>
       <c r="AD46"/>
       <c r="AE46"/>
@@ -11300,7 +11485,11 @@
       <c r="BB46"/>
       <c r="BC46"/>
       <c r="BD46"/>
-      <c r="BE46"/>
+      <c r="BE46" t="inlineStr">
+        <is>
+          <t>/kibana/s/governance/app/dashboards#/view/c6a08800-fe67-11ee-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
+        </is>
+      </c>
       <c r="BF46"/>
       <c r="BG46"/>
       <c r="BH46"/>
@@ -11315,11 +11504,11 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E47"/>
@@ -11345,7 +11534,11 @@
       <c r="Y47"/>
       <c r="Z47"/>
       <c r="AA47"/>
-      <c r="AB47"/>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Vulnerabilities p/ State</t>
+        </is>
+      </c>
       <c r="AC47"/>
       <c r="AD47"/>
       <c r="AE47"/>
@@ -11389,11 +11582,11 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E48"/>
@@ -11419,23 +11612,9 @@
       <c r="Y48"/>
       <c r="Z48"/>
       <c r="AA48"/>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>&lt;div &gt;
-&lt;a href="/recordm/index.html#/instance/create/54" onclick="" class="text-white bg-green-700 hover:bg-green-800 focus:outline-none focus:ring-4 focus:ring-green-300 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 dark:bg-green-600 dark:hover:bg-green-700 dark:focus:ring-green-800 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-house-crack fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;Register Vulnerability&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
-&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>text-center font-bold pb-2 pt-2</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB48"/>
+      <c r="AC48"/>
+      <c r="AD48"/>
       <c r="AE48"/>
       <c r="AF48"/>
       <c r="AG48"/>
@@ -11474,14 +11653,14 @@
         <v>402145.0</v>
       </c>
       <c r="B49" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E49"/>
@@ -11507,9 +11686,23 @@
       <c r="Y49"/>
       <c r="Z49"/>
       <c r="AA49"/>
-      <c r="AB49"/>
-      <c r="AC49"/>
-      <c r="AD49"/>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>&lt;div &gt;
+&lt;a href="/recordm/index.html#/instance/create/54" onclick="" class="text-white bg-green-700 hover:bg-green-800 focus:outline-none focus:ring-4 focus:ring-green-300 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 dark:bg-green-600 dark:hover:bg-green-700 dark:focus:ring-green-800 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-house-crack fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;Register Vulnerability&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>text-center font-bold pb-2 pt-2</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE49"/>
       <c r="AF49"/>
       <c r="AG49"/>
@@ -11536,11 +11729,7 @@
       <c r="BB49"/>
       <c r="BC49"/>
       <c r="BD49"/>
-      <c r="BE49" t="inlineStr">
-        <is>
-          <t>/kibana/s/governance/app/dashboards#/view/8ca24640-147c-11ef-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
-        </is>
-      </c>
+      <c r="BE49"/>
       <c r="BF49"/>
       <c r="BG49"/>
       <c r="BH49"/>
@@ -11549,17 +11738,17 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>402144.0</v>
+        <v>402145.0</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C50" t="n">
         <v>0.0</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="E50"/>
@@ -11585,22 +11774,9 @@
       <c r="Y50"/>
       <c r="Z50"/>
       <c r="AA50"/>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>Incidents
-&lt;hr class="mt-1 h-px bg-gray-200 border-0 dark:bg-gray-700"&gt;</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>text-center font-bold pb-2 text-xl</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB50"/>
+      <c r="AC50"/>
+      <c r="AD50"/>
       <c r="AE50"/>
       <c r="AF50"/>
       <c r="AG50"/>
@@ -11627,7 +11803,11 @@
       <c r="BB50"/>
       <c r="BC50"/>
       <c r="BD50"/>
-      <c r="BE50"/>
+      <c r="BE50" t="inlineStr">
+        <is>
+          <t>/kibana/s/governance/app/dashboards#/view/8ca24640-147c-11ef-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
+        </is>
+      </c>
       <c r="BF50"/>
       <c r="BG50"/>
       <c r="BH50"/>
@@ -11642,11 +11822,11 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E51"/>
@@ -11672,9 +11852,22 @@
       <c r="Y51"/>
       <c r="Z51"/>
       <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51"/>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Incidents
+&lt;hr class="mt-1 h-px bg-gray-200 border-0 dark:bg-gray-700"&gt;</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>text-center font-bold pb-2 text-xl</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE51"/>
       <c r="AF51"/>
       <c r="AG51"/>
@@ -11716,11 +11909,11 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E52"/>
@@ -11746,13 +11939,7 @@
       <c r="Y52"/>
       <c r="Z52"/>
       <c r="AA52"/>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;
-&lt;a href="/recordm/index.html#/instance/create/16" onclick="" class="text-white bg-green-700 hover:bg-green-800 focus:outline-none focus:ring-4 focus:ring-green-300 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 dark:bg-green-600 dark:hover:bg-green-700 dark:focus:ring-green-800 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-person-falling-burst fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;Register Incident&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
-&lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="AB52"/>
       <c r="AC52"/>
       <c r="AD52"/>
       <c r="AE52"/>
@@ -11790,13 +11977,13 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>402143.0</v>
+        <v>402144.0</v>
       </c>
       <c r="B53" t="n">
         <v>0.0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -11828,7 +12015,9 @@
       <c r="AA53"/>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Threats p/ Type</t>
+          <t>&lt;div&gt;
+&lt;a href="/recordm/index.html#/instance/create/16" onclick="" class="text-white bg-green-700 hover:bg-green-800 focus:outline-none focus:ring-4 focus:ring-green-300 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 dark:bg-green-600 dark:hover:bg-green-700 dark:focus:ring-green-800 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-person-falling-burst fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;Register Incident&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
+&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AC53"/>
@@ -11874,11 +12063,11 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E54"/>
@@ -11904,7 +12093,11 @@
       <c r="Y54"/>
       <c r="Z54"/>
       <c r="AA54"/>
-      <c r="AB54"/>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Threats p/ Type</t>
+        </is>
+      </c>
       <c r="AC54"/>
       <c r="AD54"/>
       <c r="AE54"/>
@@ -11945,14 +12138,14 @@
         <v>402143.0</v>
       </c>
       <c r="B55" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E55"/>
@@ -11978,11 +12171,7 @@
       <c r="Y55"/>
       <c r="Z55"/>
       <c r="AA55"/>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>Threats p/ Origin</t>
-        </is>
-      </c>
+      <c r="AB55"/>
       <c r="AC55"/>
       <c r="AD55"/>
       <c r="AE55"/>
@@ -12026,11 +12215,11 @@
         <v>1.0</v>
       </c>
       <c r="C56" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E56"/>
@@ -12056,7 +12245,11 @@
       <c r="Y56"/>
       <c r="Z56"/>
       <c r="AA56"/>
-      <c r="AB56"/>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Threats p/ Origin</t>
+        </is>
+      </c>
       <c r="AC56"/>
       <c r="AD56"/>
       <c r="AE56"/>
@@ -12100,11 +12293,11 @@
         <v>1.0</v>
       </c>
       <c r="C57" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E57"/>
@@ -12130,11 +12323,7 @@
       <c r="Y57"/>
       <c r="Z57"/>
       <c r="AA57"/>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>Total Registered Threats</t>
-        </is>
-      </c>
+      <c r="AB57"/>
       <c r="AC57"/>
       <c r="AD57"/>
       <c r="AE57"/>
@@ -12178,11 +12367,11 @@
         <v>1.0</v>
       </c>
       <c r="C58" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E58"/>
@@ -12208,7 +12397,11 @@
       <c r="Y58"/>
       <c r="Z58"/>
       <c r="AA58"/>
-      <c r="AB58"/>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Total Registered Threats</t>
+        </is>
+      </c>
       <c r="AC58"/>
       <c r="AD58"/>
       <c r="AE58"/>
@@ -12252,11 +12445,11 @@
         <v>1.0</v>
       </c>
       <c r="C59" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E59"/>
@@ -12282,13 +12475,7 @@
       <c r="Y59"/>
       <c r="Z59"/>
       <c r="AA59"/>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>&lt;div class=""&gt;
-&lt;a href="/recordm/index.html#/instance/create/52" onclick="" class="text-white bg-green-700 hover:bg-green-800 focus:outline-none focus:ring-4 focus:ring-green-300 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 dark:bg-green-600 dark:hover:bg-green-700 dark:focus:ring-green-800 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-radiation fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;Register New Threat&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
-&lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="AB59"/>
       <c r="AC59"/>
       <c r="AD59"/>
       <c r="AE59"/>
@@ -12329,14 +12516,14 @@
         <v>402143.0</v>
       </c>
       <c r="B60" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E60"/>
@@ -12351,11 +12538,7 @@
       <c r="N60"/>
       <c r="O60"/>
       <c r="P60"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
+      <c r="Q60"/>
       <c r="R60"/>
       <c r="S60"/>
       <c r="T60"/>
@@ -12366,7 +12549,13 @@
       <c r="Y60"/>
       <c r="Z60"/>
       <c r="AA60"/>
-      <c r="AB60"/>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>&lt;div class=""&gt;
+&lt;a href="/recordm/index.html#/instance/create/52" onclick="" class="text-white bg-green-700 hover:bg-green-800 focus:outline-none focus:ring-4 focus:ring-green-300 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 dark:bg-green-600 dark:hover:bg-green-700 dark:focus:ring-green-800 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-radiation fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;Register New Threat&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="AC60"/>
       <c r="AD60"/>
       <c r="AE60"/>
@@ -12387,20 +12576,12 @@
       <c r="AT60"/>
       <c r="AU60"/>
       <c r="AV60"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>threatsSearch</t>
-        </is>
-      </c>
+      <c r="AW60"/>
       <c r="AX60"/>
       <c r="AY60"/>
       <c r="AZ60"/>
       <c r="BA60"/>
-      <c r="BB60" t="inlineStr">
-        <is>
-          <t>Search Threats...</t>
-        </is>
-      </c>
+      <c r="BB60"/>
       <c r="BC60"/>
       <c r="BD60"/>
       <c r="BE60"/>
@@ -12415,14 +12596,14 @@
         <v>402143.0</v>
       </c>
       <c r="B61" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C61" t="n">
         <v>0.0</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="E61"/>
@@ -12437,7 +12618,11 @@
       <c r="N61"/>
       <c r="O61"/>
       <c r="P61"/>
-      <c r="Q61"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
       <c r="R61"/>
       <c r="S61"/>
       <c r="T61"/>
@@ -12446,11 +12631,7 @@
       <c r="W61"/>
       <c r="X61"/>
       <c r="Y61"/>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>InputVar</t>
-        </is>
-      </c>
+      <c r="Z61"/>
       <c r="AA61"/>
       <c r="AB61"/>
       <c r="AC61"/>
@@ -12473,19 +12654,23 @@
       <c r="AT61"/>
       <c r="AU61"/>
       <c r="AV61"/>
-      <c r="AW61"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>threatsSearch</t>
+        </is>
+      </c>
       <c r="AX61"/>
       <c r="AY61"/>
       <c r="AZ61"/>
       <c r="BA61"/>
-      <c r="BB61"/>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>Search Threats...</t>
+        </is>
+      </c>
       <c r="BC61"/>
       <c r="BD61"/>
-      <c r="BE61" t="inlineStr">
-        <is>
-          <t>/kibana/s/governance/app/dashboards#/view/20835b40-089a-11ef-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
-        </is>
-      </c>
+      <c r="BE61"/>
       <c r="BF61"/>
       <c r="BG61"/>
       <c r="BH61"/>
@@ -12494,17 +12679,17 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>402142.0</v>
+        <v>402143.0</v>
       </c>
       <c r="B62" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="C62" t="n">
         <v>0.0</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="E62"/>
@@ -12528,13 +12713,13 @@
       <c r="W62"/>
       <c r="X62"/>
       <c r="Y62"/>
-      <c r="Z62"/>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>InputVar</t>
+        </is>
+      </c>
       <c r="AA62"/>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>Detected Findings</t>
-        </is>
-      </c>
+      <c r="AB62"/>
       <c r="AC62"/>
       <c r="AD62"/>
       <c r="AE62"/>
@@ -12563,7 +12748,11 @@
       <c r="BB62"/>
       <c r="BC62"/>
       <c r="BD62"/>
-      <c r="BE62"/>
+      <c r="BE62" t="inlineStr">
+        <is>
+          <t>/kibana/s/governance/app/dashboards#/view/20835b40-089a-11ef-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
+        </is>
+      </c>
       <c r="BF62"/>
       <c r="BG62"/>
       <c r="BH62"/>
@@ -12578,11 +12767,11 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E63"/>
@@ -12608,7 +12797,11 @@
       <c r="Y63"/>
       <c r="Z63"/>
       <c r="AA63"/>
-      <c r="AB63"/>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Detected Findings</t>
+        </is>
+      </c>
       <c r="AC63"/>
       <c r="AD63"/>
       <c r="AE63"/>
@@ -12652,11 +12845,11 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E64"/>
@@ -12682,13 +12875,7 @@
       <c r="Y64"/>
       <c r="Z64"/>
       <c r="AA64"/>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>&lt;div class=""&gt;
-&lt;a href="/recordm/index.html#/instance/create/31" onclick="" class="text-white bg-green-700 hover:bg-green-800 focus:outline-none focus:ring-4 focus:ring-green-300 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 dark:bg-green-600 dark:hover:bg-green-700 dark:focus:ring-green-800 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-clipboard-question fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;Register Finding&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
-&lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="AB64"/>
       <c r="AC64"/>
       <c r="AD64"/>
       <c r="AE64"/>
@@ -12729,14 +12916,14 @@
         <v>402142.0</v>
       </c>
       <c r="B65" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E65"/>
@@ -12751,11 +12938,7 @@
       <c r="N65"/>
       <c r="O65"/>
       <c r="P65"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
+      <c r="Q65"/>
       <c r="R65"/>
       <c r="S65"/>
       <c r="T65"/>
@@ -12766,7 +12949,13 @@
       <c r="Y65"/>
       <c r="Z65"/>
       <c r="AA65"/>
-      <c r="AB65"/>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>&lt;div class=""&gt;
+&lt;a href="/recordm/index.html#/instance/create/31" onclick="" class="text-white bg-green-700 hover:bg-green-800 focus:outline-none focus:ring-4 focus:ring-green-300 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 dark:bg-green-600 dark:hover:bg-green-700 dark:focus:ring-green-800 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-clipboard-question fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;Register Finding&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="AC65"/>
       <c r="AD65"/>
       <c r="AE65"/>
@@ -12787,20 +12976,12 @@
       <c r="AT65"/>
       <c r="AU65"/>
       <c r="AV65"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
+      <c r="AW65"/>
       <c r="AX65"/>
       <c r="AY65"/>
       <c r="AZ65"/>
       <c r="BA65"/>
-      <c r="BB65" t="inlineStr">
-        <is>
-          <t>Pesquisar Controlos...</t>
-        </is>
-      </c>
+      <c r="BB65"/>
       <c r="BC65"/>
       <c r="BD65"/>
       <c r="BE65"/>
@@ -12815,14 +12996,14 @@
         <v>402142.0</v>
       </c>
       <c r="B66" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C66" t="n">
         <v>0.0</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="E66"/>
@@ -12837,7 +13018,11 @@
       <c r="N66"/>
       <c r="O66"/>
       <c r="P66"/>
-      <c r="Q66"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
       <c r="R66"/>
       <c r="S66"/>
       <c r="T66"/>
@@ -12846,11 +13031,7 @@
       <c r="W66"/>
       <c r="X66"/>
       <c r="Y66"/>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>InputVar</t>
-        </is>
-      </c>
+      <c r="Z66"/>
       <c r="AA66"/>
       <c r="AB66"/>
       <c r="AC66"/>
@@ -12873,19 +13054,23 @@
       <c r="AT66"/>
       <c r="AU66"/>
       <c r="AV66"/>
-      <c r="AW66"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
       <c r="AX66"/>
       <c r="AY66"/>
       <c r="AZ66"/>
       <c r="BA66"/>
-      <c r="BB66"/>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>Pesquisar Controlos...</t>
+        </is>
+      </c>
       <c r="BC66"/>
       <c r="BD66"/>
-      <c r="BE66" t="inlineStr">
-        <is>
-          <t>/kibana/s/governance/app/dashboards#/view/1577dad0-fbdb-11ee-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
-        </is>
-      </c>
+      <c r="BE66"/>
       <c r="BF66"/>
       <c r="BG66"/>
       <c r="BH66"/>
@@ -12894,17 +13079,17 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>402141.0</v>
+        <v>402142.0</v>
       </c>
       <c r="B67" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C67" t="n">
         <v>0.0</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="E67"/>
@@ -12928,14 +13113,13 @@
       <c r="W67"/>
       <c r="X67"/>
       <c r="Y67"/>
-      <c r="Z67"/>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>InputVar</t>
+        </is>
+      </c>
       <c r="AA67"/>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>Owner's Consent
-&lt;hr class="mt-1 h-px bg-gray-200 border-0 dark:bg-gray-700"&gt;</t>
-        </is>
-      </c>
+      <c r="AB67"/>
       <c r="AC67"/>
       <c r="AD67"/>
       <c r="AE67"/>
@@ -12964,7 +13148,11 @@
       <c r="BB67"/>
       <c r="BC67"/>
       <c r="BD67"/>
-      <c r="BE67"/>
+      <c r="BE67" t="inlineStr">
+        <is>
+          <t>/kibana/s/governance/app/dashboards#/view/1577dad0-fbdb-11ee-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
+        </is>
+      </c>
       <c r="BF67"/>
       <c r="BG67"/>
       <c r="BH67"/>
@@ -12979,11 +13167,11 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E68"/>
@@ -13009,7 +13197,12 @@
       <c r="Y68"/>
       <c r="Z68"/>
       <c r="AA68"/>
-      <c r="AB68"/>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Owner's Consent
+&lt;hr class="mt-1 h-px bg-gray-200 border-0 dark:bg-gray-700"&gt;</t>
+        </is>
+      </c>
       <c r="AC68"/>
       <c r="AD68"/>
       <c r="AE68"/>
@@ -13053,11 +13246,11 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E69"/>
@@ -13083,12 +13276,7 @@
       <c r="Y69"/>
       <c r="Z69"/>
       <c r="AA69"/>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>Data Owner's Requests
-&lt;hr class="mt-1 h-px bg-gray-200 border-0 dark:bg-gray-700"&gt;</t>
-        </is>
-      </c>
+      <c r="AB69"/>
       <c r="AC69"/>
       <c r="AD69"/>
       <c r="AE69"/>
@@ -13132,11 +13320,11 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E70"/>
@@ -13162,7 +13350,12 @@
       <c r="Y70"/>
       <c r="Z70"/>
       <c r="AA70"/>
-      <c r="AB70"/>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Data Owner's Requests
+&lt;hr class="mt-1 h-px bg-gray-200 border-0 dark:bg-gray-700"&gt;</t>
+        </is>
+      </c>
       <c r="AC70"/>
       <c r="AD70"/>
       <c r="AE70"/>
@@ -13200,17 +13393,17 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>402140.0</v>
+        <v>402141.0</v>
       </c>
       <c r="B71" t="n">
         <v>0.0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E71"/>
@@ -13236,11 +13429,7 @@
       <c r="Y71"/>
       <c r="Z71"/>
       <c r="AA71"/>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>Treatment Activities</t>
-        </is>
-      </c>
+      <c r="AB71"/>
       <c r="AC71"/>
       <c r="AD71"/>
       <c r="AE71"/>
@@ -13284,7 +13473,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -13316,20 +13505,11 @@
       <c r="AA72"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Registration of business activity. It includes data processing rules and policies, as well as the underlying logic.
-&lt;hr class="mt-1 h-px bg-gray-200 border-0 dark:bg-gray-700"&gt;</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>pb-2 text-justify</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+          <t>Treatment Activities</t>
+        </is>
+      </c>
+      <c r="AC72"/>
+      <c r="AD72"/>
       <c r="AE72"/>
       <c r="AF72"/>
       <c r="AG72"/>
@@ -13371,11 +13551,11 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E73"/>
@@ -13401,9 +13581,22 @@
       <c r="Y73"/>
       <c r="Z73"/>
       <c r="AA73"/>
-      <c r="AB73"/>
-      <c r="AC73"/>
-      <c r="AD73"/>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Registration of business activity. It includes data processing rules and policies, as well as the underlying logic.
+&lt;hr class="mt-1 h-px bg-gray-200 border-0 dark:bg-gray-700"&gt;</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>pb-2 text-justify</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE73"/>
       <c r="AF73"/>
       <c r="AG73"/>
@@ -13434,16 +13627,8 @@
       <c r="BF73"/>
       <c r="BG73"/>
       <c r="BH73"/>
-      <c r="BI73" t="inlineStr">
-        <is>
-          <t>w-full table-auto</t>
-        </is>
-      </c>
-      <c r="BJ73" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="BI73"/>
+      <c r="BJ73"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -13453,11 +13638,11 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Menu</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E74"/>
@@ -13495,16 +13680,8 @@
       <c r="AK74"/>
       <c r="AL74"/>
       <c r="AM74"/>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>flex  gap-y-2 justify-center</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AN74"/>
+      <c r="AO74"/>
       <c r="AP74"/>
       <c r="AQ74"/>
       <c r="AR74"/>
@@ -13524,8 +13701,16 @@
       <c r="BF74"/>
       <c r="BG74"/>
       <c r="BH74"/>
-      <c r="BI74"/>
-      <c r="BJ74"/>
+      <c r="BI74" t="inlineStr">
+        <is>
+          <t>w-full table-auto</t>
+        </is>
+      </c>
+      <c r="BJ74" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -13535,11 +13720,11 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ModalActivator</t>
+          <t>Menu</t>
         </is>
       </c>
       <c r="E75"/>
@@ -13577,29 +13762,21 @@
       <c r="AK75"/>
       <c r="AL75"/>
       <c r="AM75"/>
-      <c r="AN75"/>
-      <c r="AO75"/>
+      <c r="AN75" t="inlineStr">
+        <is>
+          <t>flex  gap-y-2 justify-center</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AP75"/>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>absolute top-2 right-2 bg-sky-800 text-white rounded-md px-2 py-1 text-sm text-center cursor-pointer hover:bg-sky-600</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>Processo</t>
-        </is>
-      </c>
-      <c r="AT75" t="inlineStr">
-        <is>
-          <t>Processo Atividades</t>
-        </is>
-      </c>
+      <c r="AQ75"/>
+      <c r="AR75"/>
+      <c r="AS75"/>
+      <c r="AT75"/>
       <c r="AU75"/>
       <c r="AV75"/>
       <c r="AW75"/>
@@ -13622,14 +13799,14 @@
         <v>402140.0</v>
       </c>
       <c r="B76" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mermaid</t>
+          <t>ModalActivator</t>
         </is>
       </c>
       <c r="E76"/>
@@ -13658,11 +13835,7 @@
       <c r="AB76"/>
       <c r="AC76"/>
       <c r="AD76"/>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>text-sm top-3 left-2 absolute text-blue-400</t>
-        </is>
-      </c>
+      <c r="AE76"/>
       <c r="AF76"/>
       <c r="AG76"/>
       <c r="AH76"/>
@@ -13673,15 +13846,27 @@
       <c r="AM76"/>
       <c r="AN76"/>
       <c r="AO76"/>
-      <c r="AP76" t="inlineStr">
-        <is>
-          <t>LinkClasses</t>
-        </is>
-      </c>
-      <c r="AQ76"/>
-      <c r="AR76"/>
-      <c r="AS76"/>
-      <c r="AT76"/>
+      <c r="AP76"/>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>absolute top-2 right-2 bg-sky-800 text-white rounded-md px-2 py-1 text-sm text-center cursor-pointer hover:bg-sky-600</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>Processo</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr">
+        <is>
+          <t>Processo Atividades</t>
+        </is>
+      </c>
       <c r="AU76"/>
       <c r="AV76"/>
       <c r="AW76"/>
@@ -13690,11 +13875,7 @@
       <c r="AZ76"/>
       <c r="BA76"/>
       <c r="BB76"/>
-      <c r="BC76" t="inlineStr">
-        <is>
-          <t>3041</t>
-        </is>
-      </c>
+      <c r="BC76"/>
       <c r="BD76"/>
       <c r="BE76"/>
       <c r="BF76"/>
@@ -13705,17 +13886,17 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>402139.0</v>
+        <v>402140.0</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C77" t="n">
         <v>0.0</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Mermaid</t>
         </is>
       </c>
       <c r="E77"/>
@@ -13741,14 +13922,14 @@
       <c r="Y77"/>
       <c r="Z77"/>
       <c r="AA77"/>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>Tipos de Conteúdos De Formação</t>
-        </is>
-      </c>
+      <c r="AB77"/>
       <c r="AC77"/>
       <c r="AD77"/>
-      <c r="AE77"/>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>text-sm top-3 left-2 absolute text-blue-400</t>
+        </is>
+      </c>
       <c r="AF77"/>
       <c r="AG77"/>
       <c r="AH77"/>
@@ -13759,7 +13940,11 @@
       <c r="AM77"/>
       <c r="AN77"/>
       <c r="AO77"/>
-      <c r="AP77"/>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>LinkClasses</t>
+        </is>
+      </c>
       <c r="AQ77"/>
       <c r="AR77"/>
       <c r="AS77"/>
@@ -13772,7 +13957,11 @@
       <c r="AZ77"/>
       <c r="BA77"/>
       <c r="BB77"/>
-      <c r="BC77"/>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>406228</t>
+        </is>
+      </c>
       <c r="BD77"/>
       <c r="BE77"/>
       <c r="BF77"/>
@@ -13789,11 +13978,11 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E78"/>
@@ -13819,7 +14008,11 @@
       <c r="Y78"/>
       <c r="Z78"/>
       <c r="AA78"/>
-      <c r="AB78"/>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Tipos de Conteúdos De Formação</t>
+        </is>
+      </c>
       <c r="AC78"/>
       <c r="AD78"/>
       <c r="AE78"/>
@@ -13860,14 +14053,14 @@
         <v>402139.0</v>
       </c>
       <c r="B79" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E79"/>
@@ -13893,11 +14086,7 @@
       <c r="Y79"/>
       <c r="Z79"/>
       <c r="AA79"/>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>Training Profile Types</t>
-        </is>
-      </c>
+      <c r="AB79"/>
       <c r="AC79"/>
       <c r="AD79"/>
       <c r="AE79"/>
@@ -13941,11 +14130,11 @@
         <v>1.0</v>
       </c>
       <c r="C80" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E80"/>
@@ -13971,7 +14160,11 @@
       <c r="Y80"/>
       <c r="Z80"/>
       <c r="AA80"/>
-      <c r="AB80"/>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Training Profile Types</t>
+        </is>
+      </c>
       <c r="AC80"/>
       <c r="AD80"/>
       <c r="AE80"/>
@@ -14012,14 +14205,14 @@
         <v>402139.0</v>
       </c>
       <c r="B81" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E81"/>
@@ -14043,11 +14236,7 @@
       <c r="W81"/>
       <c r="X81"/>
       <c r="Y81"/>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>InputVar</t>
-        </is>
-      </c>
+      <c r="Z81"/>
       <c r="AA81"/>
       <c r="AB81"/>
       <c r="AC81"/>
@@ -14078,11 +14267,7 @@
       <c r="BB81"/>
       <c r="BC81"/>
       <c r="BD81"/>
-      <c r="BE81" t="inlineStr">
-        <is>
-          <t>/kibana/s/governance/app/dashboards#/view/e5717600-f8a3-11ee-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
-        </is>
-      </c>
+      <c r="BE81"/>
       <c r="BF81"/>
       <c r="BG81"/>
       <c r="BH81"/>
@@ -14091,17 +14276,17 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>402138.0</v>
+        <v>402139.0</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C82" t="n">
         <v>0.0</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="E82"/>
@@ -14125,33 +14310,15 @@
       <c r="W82"/>
       <c r="X82"/>
       <c r="Y82"/>
-      <c r="Z82"/>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>InputVar</t>
+        </is>
+      </c>
       <c r="AA82"/>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>&lt;div class="grid grid-flow-row-dense md:grid-cols-12 pb-2 border-b-2 border-black"&gt;
-&lt;a class="md:col-span-4"&gt;
-  &lt;img class="border border-black rounded-md" src="/recordm/recordm/instances/408014/files/5653/modulo2.png" alt="Visit the CoB Learning site" width="300" height="300"/&gt;
-&lt;/a&gt;
-&lt;div class=" col-span-12 md:col-span-8 pl-2"&gt;
-&lt;div class="text-2xl text-left font-bold"&gt;GDPR Awareness Training&lt;/div&gt;
-&lt;div class="text-left text-base pb-1 pt-1 text-justify font-normal"&gt;
-Understanding GDPR is vital for employees. It ensures responsible handling of personal data, complying with legal requirements and protecting the company's reputation. Emphasizing transparency and minimal data usage, GDPR awareness enables better customer service and positions the company responsibly in the global arena. In essence, it's about contributing to a secure and trustworthy organizational culture.
-&lt;/div&gt;
-&lt;/div&gt;
-&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>text-left pb-2 text-4xl</t>
-        </is>
-      </c>
-      <c r="AD82" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB82"/>
+      <c r="AC82"/>
+      <c r="AD82"/>
       <c r="AE82"/>
       <c r="AF82"/>
       <c r="AG82"/>
@@ -14178,7 +14345,11 @@
       <c r="BB82"/>
       <c r="BC82"/>
       <c r="BD82"/>
-      <c r="BE82"/>
+      <c r="BE82" t="inlineStr">
+        <is>
+          <t>/kibana/s/governance/app/dashboards#/view/e5717600-f8a3-11ee-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
+        </is>
+      </c>
       <c r="BF82"/>
       <c r="BG82"/>
       <c r="BH82"/>
@@ -14190,7 +14361,7 @@
         <v>402138.0</v>
       </c>
       <c r="B83" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C83" t="n">
         <v>0.0</v>
@@ -14225,16 +14396,22 @@
       <c r="AA83"/>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>{{#if (eq ../user.username 'rvalverde')}}
-&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
-{{else}}
-{{título_conteúdo}}
-{{/if}}</t>
+          <t>&lt;div class="grid grid-flow-row-dense md:grid-cols-12 pb-2 border-b-2 border-black"&gt;
+&lt;a class="md:col-span-4"&gt;
+  &lt;img class="border border-black rounded-md" src="/recordm/recordm/instances/408014/files/5653/modulo2.png" alt="Visit the CoB Learning site" width="300" height="300"/&gt;
+&lt;/a&gt;
+&lt;div class=" col-span-12 md:col-span-8 pl-2"&gt;
+&lt;div class="text-2xl text-left font-bold"&gt;GDPR Awareness Training&lt;/div&gt;
+&lt;div class="text-left text-base pb-1 pt-1 text-justify font-normal"&gt;
+Understanding GDPR is vital for employees. It ensures responsible handling of personal data, complying with legal requirements and protecting the company's reputation. Emphasizing transparency and minimal data usage, GDPR awareness enables better customer service and positions the company responsibly in the global arena. In essence, it's about contributing to a secure and trustworthy organizational culture.
+&lt;/div&gt;
+&lt;/div&gt;
+&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>text-black text-2xl font-bold flex-none</t>
+          <t>text-left pb-2 text-4xl</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
@@ -14283,7 +14460,7 @@
         <v>1.0</v>
       </c>
       <c r="C84" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -14315,12 +14492,16 @@
       <c r="AA84"/>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>{{resumo_conteúdo}}</t>
+          <t>{{#if (eq ../user.username 'rvalverde')}}
+&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
+{{else}}
+{{título_conteúdo}}
+{{/if}}</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>text-left pb-2 flex-grow pt-2</t>
+          <t>text-black text-2xl font-bold flex-none</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
@@ -14369,11 +14550,11 @@
         <v>1.0</v>
       </c>
       <c r="C85" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ModalActivator</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E85"/>
@@ -14399,9 +14580,21 @@
       <c r="Y85"/>
       <c r="Z85"/>
       <c r="AA85"/>
-      <c r="AB85"/>
-      <c r="AC85"/>
-      <c r="AD85"/>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>{{resumo_conteúdo}}</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>text-left pb-2 flex-grow pt-2</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE85"/>
       <c r="AF85"/>
       <c r="AG85"/>
@@ -14414,26 +14607,10 @@
       <c r="AN85"/>
       <c r="AO85"/>
       <c r="AP85"/>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>cursor-pointer text-sm flex-none</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
-        </is>
-      </c>
-      <c r="AT85" t="inlineStr">
-        <is>
-          <t>{{id}}</t>
-        </is>
-      </c>
+      <c r="AQ85"/>
+      <c r="AR85"/>
+      <c r="AS85"/>
+      <c r="AT85"/>
       <c r="AU85"/>
       <c r="AV85"/>
       <c r="AW85"/>
@@ -14456,25 +14633,21 @@
         <v>402138.0</v>
       </c>
       <c r="B86" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C86" t="n">
         <v>2.0</v>
       </c>
-      <c r="C86" t="n">
-        <v>0.0</v>
-      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Slides</t>
+          <t>ModalActivator</t>
         </is>
       </c>
       <c r="E86"/>
       <c r="F86"/>
       <c r="G86"/>
       <c r="H86"/>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>{{markdown_conteúdo}}</t>
-        </is>
-      </c>
+      <c r="I86"/>
       <c r="J86"/>
       <c r="K86"/>
       <c r="L86"/>
@@ -14508,10 +14681,26 @@
       <c r="AN86"/>
       <c r="AO86"/>
       <c r="AP86"/>
-      <c r="AQ86"/>
-      <c r="AR86"/>
-      <c r="AS86"/>
-      <c r="AT86"/>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>cursor-pointer text-sm flex-none</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr">
+        <is>
+          <t>{{id}}</t>
+        </is>
+      </c>
       <c r="AU86"/>
       <c r="AV86"/>
       <c r="AW86"/>
@@ -14534,21 +14723,25 @@
         <v>402138.0</v>
       </c>
       <c r="B87" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C87" t="n">
         <v>0.0</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Slides</t>
         </is>
       </c>
       <c r="E87"/>
       <c r="F87"/>
       <c r="G87"/>
       <c r="H87"/>
-      <c r="I87"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>{{markdown_conteúdo}}</t>
+        </is>
+      </c>
       <c r="J87"/>
       <c r="K87"/>
       <c r="L87"/>
@@ -14567,25 +14760,9 @@
       <c r="Y87"/>
       <c r="Z87"/>
       <c r="AA87"/>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>{{#if (eq ../user.username 'rvalverde')}}
-&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
-{{else}}
-{{not_seen.value.0.título_conteúdo}}
-{{/if}}</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>text-black text-2xl font-bold flex-none</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB87"/>
+      <c r="AC87"/>
+      <c r="AD87"/>
       <c r="AE87"/>
       <c r="AF87"/>
       <c r="AG87"/>
@@ -14627,7 +14804,7 @@
         <v>3.0</v>
       </c>
       <c r="C88" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -14659,12 +14836,16 @@
       <c r="AA88"/>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>{{not_seen.value.0.resumo_conteúdo}}</t>
+          <t>{{#if (eq ../user.username 'rvalverde')}}
+&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
+{{else}}
+{{not_seen.value.0.título_conteúdo}}
+{{/if}}</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>text-left pb-2 flex-grow pt-2</t>
+          <t>text-black text-2xl font-bold flex-none</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -14713,11 +14894,11 @@
         <v>3.0</v>
       </c>
       <c r="C89" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ModalActivator</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E89"/>
@@ -14743,9 +14924,21 @@
       <c r="Y89"/>
       <c r="Z89"/>
       <c r="AA89"/>
-      <c r="AB89"/>
-      <c r="AC89"/>
-      <c r="AD89"/>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>{{not_seen.value.0.resumo_conteúdo}}</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>text-left pb-2 flex-grow pt-2</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE89"/>
       <c r="AF89"/>
       <c r="AG89"/>
@@ -14758,26 +14951,10 @@
       <c r="AN89"/>
       <c r="AO89"/>
       <c r="AP89"/>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>cursor-pointer text-sm flex-none</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr">
-        <is>
-          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
-        </is>
-      </c>
-      <c r="AT89" t="inlineStr">
-        <is>
-          <t>{{not_seen.value.0.id}}</t>
-        </is>
-      </c>
+      <c r="AQ89"/>
+      <c r="AR89"/>
+      <c r="AS89"/>
+      <c r="AT89"/>
       <c r="AU89"/>
       <c r="AV89"/>
       <c r="AW89"/>
@@ -14800,29 +14977,21 @@
         <v>402138.0</v>
       </c>
       <c r="B90" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Slides</t>
+          <t>ModalActivator</t>
         </is>
       </c>
       <c r="E90"/>
       <c r="F90"/>
       <c r="G90"/>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>gov_slides_feeditem_update</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>{{#if not_seen}}{{not_seen.value.0.markdown_conteúdo}}{{/if}}</t>
-        </is>
-      </c>
+      <c r="H90"/>
+      <c r="I90"/>
       <c r="J90"/>
       <c r="K90"/>
       <c r="L90"/>
@@ -14856,10 +15025,26 @@
       <c r="AN90"/>
       <c r="AO90"/>
       <c r="AP90"/>
-      <c r="AQ90"/>
-      <c r="AR90"/>
-      <c r="AS90"/>
-      <c r="AT90"/>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>cursor-pointer text-sm flex-none</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr">
+        <is>
+          <t>{{not_seen.value.0.id}}</t>
+        </is>
+      </c>
       <c r="AU90"/>
       <c r="AV90"/>
       <c r="AW90"/>
@@ -14872,35 +15057,39 @@
       <c r="BD90"/>
       <c r="BE90"/>
       <c r="BF90"/>
-      <c r="BG90" t="inlineStr">
-        <is>
-          <t>EndOfContentTrigger</t>
-        </is>
-      </c>
+      <c r="BG90"/>
       <c r="BH90"/>
       <c r="BI90"/>
       <c r="BJ90"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>402137.0</v>
+        <v>402138.0</v>
       </c>
       <c r="B91" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="C91" t="n">
         <v>0.0</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Slides</t>
         </is>
       </c>
       <c r="E91"/>
       <c r="F91"/>
       <c r="G91"/>
-      <c r="H91"/>
-      <c r="I91"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>gov_slides_feeditem_update</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>{{#if not_seen}}{{not_seen.value.0.markdown_conteúdo}}{{/if}}</t>
+        </is>
+      </c>
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91"/>
@@ -14919,37 +15108,9 @@
       <c r="Y91"/>
       <c r="Z91"/>
       <c r="AA91"/>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>&lt;div class="grid grid-flow-row-dense md:grid-cols-12 pb-2 border-b-2 border-black "&gt;
-&lt;a class="md:col-span-4" href="/recordm/recordm/instances/408013/files/5653/modulo1.png"&gt;
-  &lt;img class="cursor-pointer border border-black rounded-md" src="/recordm/recordm/instances/408013/files/5653/modulo1.png" alt="Visit the CoB Learning site" width="300" height="300"/&gt;
-&lt;/a&gt;
-&lt;div class=" col-span-12 md:col-span-8 pl-2"&gt;
-&lt;div class="text-2xl text-left font-bold"&gt;Security Conformity Solution Introduction &lt;/div&gt;
-&lt;div class="text-left text-base pb-1 pt-1 text-justify font-normal"&gt;
-Our solution's goal is to implement an ISMS (Information Security Management System). An ISMS is a set of policies, principles or procedures used to identify risks and define risk mitigation steps. 
-&lt;br&gt;
-&lt;br&gt;
-Here, we will guide you through the initial setup and introductory contents, to learn the "why" and "how" of each part of our solution.
-&lt;br&gt;
-&lt;br&gt;
-&lt;span class="font-bold"&gt;Please follow the "Next steps" specified below&lt;/span&gt;. Once you've completed a step, &lt;span class="font-bold "&gt;please be sure to click "Complete"&lt;/span&gt;. After refreshing the page, the next step will appear. 
-&lt;/div&gt;
-&lt;/div&gt;
-&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>text-left pb-2 text-4xl text-black</t>
-        </is>
-      </c>
-      <c r="AD91" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB91"/>
+      <c r="AC91"/>
+      <c r="AD91"/>
       <c r="AE91"/>
       <c r="AF91"/>
       <c r="AG91"/>
@@ -14978,7 +15139,11 @@
       <c r="BD91"/>
       <c r="BE91"/>
       <c r="BF91"/>
-      <c r="BG91"/>
+      <c r="BG91" t="inlineStr">
+        <is>
+          <t>EndOfContentTrigger</t>
+        </is>
+      </c>
       <c r="BH91"/>
       <c r="BI91"/>
       <c r="BJ91"/>
@@ -14988,7 +15153,7 @@
         <v>402137.0</v>
       </c>
       <c r="B92" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C92" t="n">
         <v>0.0</v>
@@ -15023,14 +15188,28 @@
       <c r="AA92"/>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>&lt;a href="/recordm/#/instance/{{mycolab.value.0.empresa}}" class="hover:text-cyan-500"&gt;
-{{mycolab.value.0.nome}} &lt;i class="fa-solid fa-link fa-xs"&gt;&lt;/i&gt;
-&lt;/a&gt;</t>
+          <t>&lt;div class="grid grid-flow-row-dense md:grid-cols-12 pb-2 border-b-2 border-black "&gt;
+&lt;a class="md:col-span-4" href="/recordm/recordm/instances/408013/files/5653/modulo1.png"&gt;
+  &lt;img class="cursor-pointer border border-black rounded-md" src="/recordm/recordm/instances/408013/files/5653/modulo1.png" alt="Visit the CoB Learning site" width="300" height="300"/&gt;
+&lt;/a&gt;
+&lt;div class=" col-span-12 md:col-span-8 pl-2"&gt;
+&lt;div class="text-2xl text-left font-bold"&gt;Security Conformity Solution Introduction &lt;/div&gt;
+&lt;div class="text-left text-base pb-1 pt-1 text-justify font-normal"&gt;
+Our solution's goal is to implement an ISMS (Information Security Management System). An ISMS is a set of policies, principles or procedures used to identify risks and define risk mitigation steps. 
+&lt;br&gt;
+&lt;br&gt;
+Here, we will guide you through the initial setup and introductory contents, to learn the "why" and "how" of each part of our solution.
+&lt;br&gt;
+&lt;br&gt;
+&lt;span class="font-bold"&gt;Please follow the "Next steps" specified below&lt;/span&gt;. Once you've completed a step, &lt;span class="font-bold "&gt;please be sure to click "Complete"&lt;/span&gt;. After refreshing the page, the next step will appear. 
+&lt;/div&gt;
+&lt;/div&gt;
+&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>text-left text-2xl text-black font-bold border-b-2 border-black mb-2</t>
+          <t>text-left pb-2 text-4xl text-black</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -15079,7 +15258,7 @@
         <v>1.0</v>
       </c>
       <c r="C93" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -15111,30 +15290,14 @@
       <c r="AA93"/>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>&lt;div&gt;
-&lt;a href="/recordm/#/instance/{{mycolab.value.0.empresa}}"&gt;
-&lt;span class="font-bold text-slate-500"&gt; {{mycolab.value.0.sigla}} &lt;/span&gt;
-&lt;/a&gt;
-&lt;/div&gt;
-&lt;br&gt;
-{{#if mycolab.value.0.username_ciso}}
-&lt;div&gt;
-&lt;span class="font-bold"&gt;CISO&lt;/span&gt;: {{mycolab.value.0.username_ciso}}
-&lt;/div&gt;
-&lt;div&gt;
-&lt;span class="font-bold"&gt;CISO Email&lt;/span&gt;: {{mycolab.value.0.email_ciso}}
-&lt;/div&gt;
-&lt;div&gt;
-&lt;span class="font-bold"&gt;Setup State&lt;/span&gt;: {{mycolab.value.0.state}}
-&lt;/div&gt;
-{{else}}
-&lt;span class="font-bold"&gt;CISO not nominated.&lt;/span&gt;
-{{/if}}</t>
+          <t>&lt;a href="/recordm/#/instance/{{mycolab.value.0.empresa}}" class="hover:text-cyan-500"&gt;
+{{mycolab.value.0.nome}} &lt;i class="fa-solid fa-link fa-xs"&gt;&lt;/i&gt;
+&lt;/a&gt;</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>text-left pb-2</t>
+          <t>text-left text-2xl text-black font-bold border-b-2 border-black mb-2</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
@@ -15180,10 +15343,10 @@
         <v>402137.0</v>
       </c>
       <c r="B94" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15215,12 +15378,30 @@
       <c r="AA94"/>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>Your next steps:</t>
+          <t>&lt;div&gt;
+&lt;a href="/recordm/#/instance/{{mycolab.value.0.empresa}}"&gt;
+&lt;span class="font-bold text-slate-500"&gt; {{mycolab.value.0.sigla}} &lt;/span&gt;
+&lt;/a&gt;
+&lt;/div&gt;
+&lt;br&gt;
+{{#if mycolab.value.0.username_ciso}}
+&lt;div&gt;
+&lt;span class="font-bold"&gt;CISO&lt;/span&gt;: {{mycolab.value.0.username_ciso}}
+&lt;/div&gt;
+&lt;div&gt;
+&lt;span class="font-bold"&gt;CISO Email&lt;/span&gt;: {{mycolab.value.0.email_ciso}}
+&lt;/div&gt;
+&lt;div&gt;
+&lt;span class="font-bold"&gt;Setup State&lt;/span&gt;: {{mycolab.value.0.state}}
+&lt;/div&gt;
+{{else}}
+&lt;span class="font-bold"&gt;CISO not nominated.&lt;/span&gt;
+{{/if}}</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>text-left text-2xl text-black font-bold</t>
+          <t>text-left pb-2</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
@@ -15269,11 +15450,11 @@
         <v>2.0</v>
       </c>
       <c r="C95" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ModalActivator</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E95"/>
@@ -15299,9 +15480,21 @@
       <c r="Y95"/>
       <c r="Z95"/>
       <c r="AA95"/>
-      <c r="AB95"/>
-      <c r="AC95"/>
-      <c r="AD95"/>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>Your next steps:</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>text-left text-2xl text-black font-bold</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE95"/>
       <c r="AF95"/>
       <c r="AG95"/>
@@ -15314,26 +15507,10 @@
       <c r="AN95"/>
       <c r="AO95"/>
       <c r="AP95"/>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>absolute top-2 right-2 bg-sky-800 text-white rounded-md px-2 py-1 text-sm text-center cursor-pointer hover:bg-sky-600</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>Processo</t>
-        </is>
-      </c>
-      <c r="AT95" t="inlineStr">
-        <is>
-          <t>Processo de Introdução</t>
-        </is>
-      </c>
+      <c r="AQ95"/>
+      <c r="AR95"/>
+      <c r="AS95"/>
+      <c r="AT95"/>
       <c r="AU95"/>
       <c r="AV95"/>
       <c r="AW95"/>
@@ -15359,11 +15536,11 @@
         <v>2.0</v>
       </c>
       <c r="C96" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>ModalActivator</t>
         </is>
       </c>
       <c r="E96"/>
@@ -15372,11 +15549,7 @@
       <c r="H96"/>
       <c r="I96"/>
       <c r="J96"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Dash</t>
-        </is>
-      </c>
+      <c r="K96"/>
       <c r="L96"/>
       <c r="M96"/>
       <c r="N96"/>
@@ -15398,21 +15571,9 @@
       <c r="AD96"/>
       <c r="AE96"/>
       <c r="AF96"/>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>SetDefaultView, ShowViews</t>
-        </is>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Work Item</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>business_process: 13 AND username:{{user.username}}</t>
-        </is>
-      </c>
+      <c r="AG96"/>
+      <c r="AH96"/>
+      <c r="AI96"/>
       <c r="AJ96"/>
       <c r="AK96"/>
       <c r="AL96"/>
@@ -15420,10 +15581,26 @@
       <c r="AN96"/>
       <c r="AO96"/>
       <c r="AP96"/>
-      <c r="AQ96"/>
-      <c r="AR96"/>
-      <c r="AS96"/>
-      <c r="AT96"/>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>absolute top-2 right-2 bg-sky-800 text-white rounded-md px-2 py-1 text-sm text-center cursor-pointer hover:bg-sky-600</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>Processo</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr">
+        <is>
+          <t>Processo de Introdução</t>
+        </is>
+      </c>
       <c r="AU96"/>
       <c r="AV96"/>
       <c r="AW96"/>
@@ -15446,14 +15623,14 @@
         <v>402137.0</v>
       </c>
       <c r="B97" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>List</t>
         </is>
       </c>
       <c r="E97"/>
@@ -15462,7 +15639,11 @@
       <c r="H97"/>
       <c r="I97"/>
       <c r="J97"/>
-      <c r="K97"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
       <c r="L97"/>
       <c r="M97"/>
       <c r="N97"/>
@@ -15479,26 +15660,26 @@
       <c r="Y97"/>
       <c r="Z97"/>
       <c r="AA97"/>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>Pesquisa de Políticas Modelo</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>text-center text-2xl text-black font-bold mb-2</t>
-        </is>
-      </c>
-      <c r="AD97" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB97"/>
+      <c r="AC97"/>
+      <c r="AD97"/>
       <c r="AE97"/>
       <c r="AF97"/>
-      <c r="AG97"/>
-      <c r="AH97"/>
-      <c r="AI97"/>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>SetDefaultView, ShowViews</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Work Item</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>business_process: 13 AND username:{{user.username}}</t>
+        </is>
+      </c>
       <c r="AJ97"/>
       <c r="AK97"/>
       <c r="AL97"/>
@@ -15535,11 +15716,11 @@
         <v>3.0</v>
       </c>
       <c r="C98" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E98"/>
@@ -15553,16 +15734,8 @@
       <c r="M98"/>
       <c r="N98"/>
       <c r="O98"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>mb-2 rounded-md px-2 w-4/5 border border-slate-400</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>Classes, Placeholder</t>
-        </is>
-      </c>
+      <c r="P98"/>
+      <c r="Q98"/>
       <c r="R98"/>
       <c r="S98"/>
       <c r="T98"/>
@@ -15573,9 +15746,21 @@
       <c r="Y98"/>
       <c r="Z98"/>
       <c r="AA98"/>
-      <c r="AB98"/>
-      <c r="AC98"/>
-      <c r="AD98"/>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>Pesquisa de Políticas Modelo</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>text-center text-2xl text-black font-bold mb-2</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE98"/>
       <c r="AF98"/>
       <c r="AG98"/>
@@ -15594,20 +15779,12 @@
       <c r="AT98"/>
       <c r="AU98"/>
       <c r="AV98"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>politicaSearch</t>
-        </is>
-      </c>
+      <c r="AW98"/>
       <c r="AX98"/>
       <c r="AY98"/>
       <c r="AZ98"/>
       <c r="BA98"/>
-      <c r="BB98" t="inlineStr">
-        <is>
-          <t>Pesquisar Políticas...</t>
-        </is>
-      </c>
+      <c r="BB98"/>
       <c r="BC98"/>
       <c r="BD98"/>
       <c r="BE98"/>
@@ -15625,11 +15802,11 @@
         <v>3.0</v>
       </c>
       <c r="C99" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="E99"/>
@@ -15638,17 +15815,21 @@
       <c r="H99"/>
       <c r="I99"/>
       <c r="J99"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>PolicyDash</t>
-        </is>
-      </c>
+      <c r="K99"/>
       <c r="L99"/>
       <c r="M99"/>
       <c r="N99"/>
       <c r="O99"/>
-      <c r="P99"/>
-      <c r="Q99"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>mb-2 rounded-md px-2 w-4/5 border border-slate-400</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Classes, Placeholder</t>
+        </is>
+      </c>
       <c r="R99"/>
       <c r="S99"/>
       <c r="T99"/>
@@ -15664,21 +15845,9 @@
       <c r="AD99"/>
       <c r="AE99"/>
       <c r="AF99"/>
-      <c r="AG99" t="inlineStr">
-        <is>
-          <t>InputVar, SetDefaultView, ShowViews</t>
-        </is>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Política</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>{{vars.politicaSearch}}</t>
-        </is>
-      </c>
+      <c r="AG99"/>
+      <c r="AH99"/>
+      <c r="AI99"/>
       <c r="AJ99"/>
       <c r="AK99"/>
       <c r="AL99"/>
@@ -15692,12 +15861,20 @@
       <c r="AT99"/>
       <c r="AU99"/>
       <c r="AV99"/>
-      <c r="AW99"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>politicaSearch</t>
+        </is>
+      </c>
       <c r="AX99"/>
       <c r="AY99"/>
       <c r="AZ99"/>
       <c r="BA99"/>
-      <c r="BB99"/>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>Pesquisar Políticas...</t>
+        </is>
+      </c>
       <c r="BC99"/>
       <c r="BD99"/>
       <c r="BE99"/>
@@ -15712,14 +15889,14 @@
         <v>402137.0</v>
       </c>
       <c r="B100" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Mermaid</t>
+          <t>List</t>
         </is>
       </c>
       <c r="E100"/>
@@ -15728,7 +15905,11 @@
       <c r="H100"/>
       <c r="I100"/>
       <c r="J100"/>
-      <c r="K100"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>PolicyDash</t>
+        </is>
+      </c>
       <c r="L100"/>
       <c r="M100"/>
       <c r="N100"/>
@@ -15748,26 +15929,30 @@
       <c r="AB100"/>
       <c r="AC100"/>
       <c r="AD100"/>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>text-sm top-3 left-2 absolute text-blue-400</t>
-        </is>
-      </c>
+      <c r="AE100"/>
       <c r="AF100"/>
-      <c r="AG100"/>
-      <c r="AH100"/>
-      <c r="AI100"/>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>InputVar, SetDefaultView, ShowViews</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Política</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>{{vars.politicaSearch}}</t>
+        </is>
+      </c>
       <c r="AJ100"/>
       <c r="AK100"/>
       <c r="AL100"/>
       <c r="AM100"/>
       <c r="AN100"/>
       <c r="AO100"/>
-      <c r="AP100" t="inlineStr">
-        <is>
-          <t>LinkClasses</t>
-        </is>
-      </c>
+      <c r="AP100"/>
       <c r="AQ100"/>
       <c r="AR100"/>
       <c r="AS100"/>
@@ -15780,11 +15965,7 @@
       <c r="AZ100"/>
       <c r="BA100"/>
       <c r="BB100"/>
-      <c r="BC100" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="BC100"/>
       <c r="BD100"/>
       <c r="BE100"/>
       <c r="BF100"/>
@@ -15795,17 +15976,17 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>402136.0</v>
+        <v>402137.0</v>
       </c>
       <c r="B101" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="C101" t="n">
         <v>0.0</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Mermaid</t>
         </is>
       </c>
       <c r="E101"/>
@@ -15831,32 +16012,14 @@
       <c r="Y101"/>
       <c r="Z101"/>
       <c r="AA101"/>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>&lt;div class="grid grid-flow-row-dense md:grid-cols-12 pb-2 border-b-2 border-black "&gt;
-&lt;a class="md:col-span-4" href="/recordm/recordm/instances/408014/files/5653/modulo2.png"&gt;
-  &lt;img class="cursor-pointer border border-black rounded-md" src="/recordm/recordm/instances/408015/files/5653/modulo3.png" alt="Visit the CoB Learning site" width="300" height="300"/&gt;
-&lt;/a&gt;
-&lt;div class=" col-span-12 md:col-span-8 pl-2"&gt;
-&lt;div class="text-2xl text-left font-bold"&gt;Cybersecurity Training&lt;/div&gt;
-&lt;div class="text-left text-base pb-1 pt-1 text-justify font-normal"&gt;
-In the digital age, ensuring strong cybersecurity practices in a company is essential. With growing reliance on technology, the risk of cyber threats looms large, threatening sensitive data, financial stability, and overall business reputation. Prioritizing cybersecurity is not only a matter of safeguarding assets but also critical for maintaining trust and operational resilience in today's interconnected business landscape.
-&lt;/div&gt;
-&lt;/div&gt;
-&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>text-left pb-2 text-4xl</t>
-        </is>
-      </c>
-      <c r="AD101" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="AE101"/>
+      <c r="AB101"/>
+      <c r="AC101"/>
+      <c r="AD101"/>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>text-sm top-3 left-2 absolute text-blue-400</t>
+        </is>
+      </c>
       <c r="AF101"/>
       <c r="AG101"/>
       <c r="AH101"/>
@@ -15867,7 +16030,11 @@
       <c r="AM101"/>
       <c r="AN101"/>
       <c r="AO101"/>
-      <c r="AP101"/>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>LinkClasses</t>
+        </is>
+      </c>
       <c r="AQ101"/>
       <c r="AR101"/>
       <c r="AS101"/>
@@ -15880,7 +16047,11 @@
       <c r="AZ101"/>
       <c r="BA101"/>
       <c r="BB101"/>
-      <c r="BC101"/>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="BD101"/>
       <c r="BE101"/>
       <c r="BF101"/>
@@ -15894,7 +16065,7 @@
         <v>402136.0</v>
       </c>
       <c r="B102" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C102" t="n">
         <v>0.0</v>
@@ -15929,16 +16100,22 @@
       <c r="AA102"/>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>{{#if (eq ../user.username 'rvalverde')}}
-&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
-{{else}}
-{{título_conteúdo}}
-{{/if}}</t>
+          <t>&lt;div class="grid grid-flow-row-dense md:grid-cols-12 pb-2 border-b-2 border-black "&gt;
+&lt;a class="md:col-span-4" href="/recordm/recordm/instances/408014/files/5653/modulo2.png"&gt;
+  &lt;img class="cursor-pointer border border-black rounded-md" src="/recordm/recordm/instances/408015/files/5653/modulo3.png" alt="Visit the CoB Learning site" width="300" height="300"/&gt;
+&lt;/a&gt;
+&lt;div class=" col-span-12 md:col-span-8 pl-2"&gt;
+&lt;div class="text-2xl text-left font-bold"&gt;Cybersecurity Training&lt;/div&gt;
+&lt;div class="text-left text-base pb-1 pt-1 text-justify font-normal"&gt;
+In the digital age, ensuring strong cybersecurity practices in a company is essential. With growing reliance on technology, the risk of cyber threats looms large, threatening sensitive data, financial stability, and overall business reputation. Prioritizing cybersecurity is not only a matter of safeguarding assets but also critical for maintaining trust and operational resilience in today's interconnected business landscape.
+&lt;/div&gt;
+&lt;/div&gt;
+&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>text-black text-2xl font-bold flex-none</t>
+          <t>text-left pb-2 text-4xl</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
@@ -15987,7 +16164,7 @@
         <v>1.0</v>
       </c>
       <c r="C103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -16019,12 +16196,16 @@
       <c r="AA103"/>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>{{resumo_conteúdo}}</t>
+          <t>{{#if (eq ../user.username 'rvalverde')}}
+&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
+{{else}}
+{{título_conteúdo}}
+{{/if}}</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>text-left pb-2 flex-grow pt-2</t>
+          <t>text-black text-2xl font-bold flex-none</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -16073,11 +16254,11 @@
         <v>1.0</v>
       </c>
       <c r="C104" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ModalActivator</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E104"/>
@@ -16103,9 +16284,21 @@
       <c r="Y104"/>
       <c r="Z104"/>
       <c r="AA104"/>
-      <c r="AB104"/>
-      <c r="AC104"/>
-      <c r="AD104"/>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>{{resumo_conteúdo}}</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>text-left pb-2 flex-grow pt-2</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE104"/>
       <c r="AF104"/>
       <c r="AG104"/>
@@ -16118,26 +16311,10 @@
       <c r="AN104"/>
       <c r="AO104"/>
       <c r="AP104"/>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>cursor-pointer text-sm flex-none</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
-        </is>
-      </c>
-      <c r="AT104" t="inlineStr">
-        <is>
-          <t>{{id}}</t>
-        </is>
-      </c>
+      <c r="AQ104"/>
+      <c r="AR104"/>
+      <c r="AS104"/>
+      <c r="AT104"/>
       <c r="AU104"/>
       <c r="AV104"/>
       <c r="AW104"/>
@@ -16160,25 +16337,21 @@
         <v>402136.0</v>
       </c>
       <c r="B105" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C105" t="n">
         <v>2.0</v>
       </c>
-      <c r="C105" t="n">
-        <v>0.0</v>
-      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Slides</t>
+          <t>ModalActivator</t>
         </is>
       </c>
       <c r="E105"/>
       <c r="F105"/>
       <c r="G105"/>
       <c r="H105"/>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>{{markdown_conteúdo}}</t>
-        </is>
-      </c>
+      <c r="I105"/>
       <c r="J105"/>
       <c r="K105"/>
       <c r="L105"/>
@@ -16212,10 +16385,26 @@
       <c r="AN105"/>
       <c r="AO105"/>
       <c r="AP105"/>
-      <c r="AQ105"/>
-      <c r="AR105"/>
-      <c r="AS105"/>
-      <c r="AT105"/>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>cursor-pointer text-sm flex-none</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr">
+        <is>
+          <t>{{id}}</t>
+        </is>
+      </c>
       <c r="AU105"/>
       <c r="AV105"/>
       <c r="AW105"/>
@@ -16238,21 +16427,25 @@
         <v>402136.0</v>
       </c>
       <c r="B106" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C106" t="n">
         <v>0.0</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Slides</t>
         </is>
       </c>
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106"/>
       <c r="H106"/>
-      <c r="I106"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>{{markdown_conteúdo}}</t>
+        </is>
+      </c>
       <c r="J106"/>
       <c r="K106"/>
       <c r="L106"/>
@@ -16271,25 +16464,9 @@
       <c r="Y106"/>
       <c r="Z106"/>
       <c r="AA106"/>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>{{#if (eq ../user.username 'rvalverde')}}
-&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
-{{else}}
-{{not_seen.value.0.título_conteúdo}}
-{{/if}}</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>text-black text-2xl font-bold flex-none</t>
-        </is>
-      </c>
-      <c r="AD106" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB106"/>
+      <c r="AC106"/>
+      <c r="AD106"/>
       <c r="AE106"/>
       <c r="AF106"/>
       <c r="AG106"/>
@@ -16331,7 +16508,7 @@
         <v>3.0</v>
       </c>
       <c r="C107" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -16363,12 +16540,16 @@
       <c r="AA107"/>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>{{not_seen.value.0.resumo_conteúdo}}</t>
+          <t>{{#if (eq ../user.username 'rvalverde')}}
+&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
+{{else}}
+{{not_seen.value.0.título_conteúdo}}
+{{/if}}</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>text-left pb-2 flex-grow pt-2</t>
+          <t>text-black text-2xl font-bold flex-none</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -16417,11 +16598,11 @@
         <v>3.0</v>
       </c>
       <c r="C108" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ModalActivator</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E108"/>
@@ -16447,9 +16628,21 @@
       <c r="Y108"/>
       <c r="Z108"/>
       <c r="AA108"/>
-      <c r="AB108"/>
-      <c r="AC108"/>
-      <c r="AD108"/>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>{{not_seen.value.0.resumo_conteúdo}}</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>text-left pb-2 flex-grow pt-2</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE108"/>
       <c r="AF108"/>
       <c r="AG108"/>
@@ -16462,26 +16655,10 @@
       <c r="AN108"/>
       <c r="AO108"/>
       <c r="AP108"/>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>cursor-pointer text-sm flex-none</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
-        </is>
-      </c>
-      <c r="AT108" t="inlineStr">
-        <is>
-          <t>{{not_seen.value.0.id}}</t>
-        </is>
-      </c>
+      <c r="AQ108"/>
+      <c r="AR108"/>
+      <c r="AS108"/>
+      <c r="AT108"/>
       <c r="AU108"/>
       <c r="AV108"/>
       <c r="AW108"/>
@@ -16504,29 +16681,21 @@
         <v>402136.0</v>
       </c>
       <c r="B109" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Slides</t>
+          <t>ModalActivator</t>
         </is>
       </c>
       <c r="E109"/>
       <c r="F109"/>
       <c r="G109"/>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>gov_slides_feeditem_update</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>{{#if not_seen}}{{not_seen.value.0.markdown_conteúdo}}{{/if}}</t>
-        </is>
-      </c>
+      <c r="H109"/>
+      <c r="I109"/>
       <c r="J109"/>
       <c r="K109"/>
       <c r="L109"/>
@@ -16560,10 +16729,26 @@
       <c r="AN109"/>
       <c r="AO109"/>
       <c r="AP109"/>
-      <c r="AQ109"/>
-      <c r="AR109"/>
-      <c r="AS109"/>
-      <c r="AT109"/>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>cursor-pointer text-sm flex-none</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr">
+        <is>
+          <t>{{not_seen.value.0.id}}</t>
+        </is>
+      </c>
       <c r="AU109"/>
       <c r="AV109"/>
       <c r="AW109"/>
@@ -16576,35 +16761,39 @@
       <c r="BD109"/>
       <c r="BE109"/>
       <c r="BF109"/>
-      <c r="BG109" t="inlineStr">
-        <is>
-          <t>EndOfContentTrigger</t>
-        </is>
-      </c>
+      <c r="BG109"/>
       <c r="BH109"/>
       <c r="BI109"/>
       <c r="BJ109"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>402135.0</v>
+        <v>402136.0</v>
       </c>
       <c r="B110" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="C110" t="n">
         <v>0.0</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Slides</t>
         </is>
       </c>
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110"/>
-      <c r="H110"/>
-      <c r="I110"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>gov_slides_feeditem_update</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>{{#if not_seen}}{{not_seen.value.0.markdown_conteúdo}}{{/if}}</t>
+        </is>
+      </c>
       <c r="J110"/>
       <c r="K110"/>
       <c r="L110"/>
@@ -16654,32 +16843,28 @@
       <c r="BD110"/>
       <c r="BE110"/>
       <c r="BF110"/>
-      <c r="BG110"/>
+      <c r="BG110" t="inlineStr">
+        <is>
+          <t>EndOfContentTrigger</t>
+        </is>
+      </c>
       <c r="BH110"/>
-      <c r="BI110" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="BJ110" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="BI110"/>
+      <c r="BJ110"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
         <v>402135.0</v>
       </c>
       <c r="B111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C111" t="n">
         <v>0.0</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E111"/>
@@ -16694,11 +16879,7 @@
       <c r="N111"/>
       <c r="O111"/>
       <c r="P111"/>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
+      <c r="Q111"/>
       <c r="R111"/>
       <c r="S111"/>
       <c r="T111"/>
@@ -16730,42 +16911,42 @@
       <c r="AT111"/>
       <c r="AU111"/>
       <c r="AV111"/>
-      <c r="AW111" t="inlineStr">
-        <is>
-          <t>politic_filter</t>
-        </is>
-      </c>
+      <c r="AW111"/>
       <c r="AX111"/>
       <c r="AY111"/>
       <c r="AZ111"/>
       <c r="BA111"/>
-      <c r="BB111" t="inlineStr">
-        <is>
-          <t>Search policies...</t>
-        </is>
-      </c>
+      <c r="BB111"/>
       <c r="BC111"/>
       <c r="BD111"/>
       <c r="BE111"/>
       <c r="BF111"/>
       <c r="BG111"/>
       <c r="BH111"/>
-      <c r="BI111"/>
-      <c r="BJ111"/>
+      <c r="BI111" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="BJ111" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
         <v>402135.0</v>
       </c>
       <c r="B112" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C112" t="n">
         <v>0.0</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="E112"/>
@@ -16780,7 +16961,11 @@
       <c r="N112"/>
       <c r="O112"/>
       <c r="P112"/>
-      <c r="Q112"/>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
       <c r="R112"/>
       <c r="S112"/>
       <c r="T112"/>
@@ -16791,7 +16976,89 @@
       <c r="Y112"/>
       <c r="Z112"/>
       <c r="AA112"/>
-      <c r="AB112" t="inlineStr">
+      <c r="AB112"/>
+      <c r="AC112"/>
+      <c r="AD112"/>
+      <c r="AE112"/>
+      <c r="AF112"/>
+      <c r="AG112"/>
+      <c r="AH112"/>
+      <c r="AI112"/>
+      <c r="AJ112"/>
+      <c r="AK112"/>
+      <c r="AL112"/>
+      <c r="AM112"/>
+      <c r="AN112"/>
+      <c r="AO112"/>
+      <c r="AP112"/>
+      <c r="AQ112"/>
+      <c r="AR112"/>
+      <c r="AS112"/>
+      <c r="AT112"/>
+      <c r="AU112"/>
+      <c r="AV112"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>politic_filter</t>
+        </is>
+      </c>
+      <c r="AX112"/>
+      <c r="AY112"/>
+      <c r="AZ112"/>
+      <c r="BA112"/>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>Search policies...</t>
+        </is>
+      </c>
+      <c r="BC112"/>
+      <c r="BD112"/>
+      <c r="BE112"/>
+      <c r="BF112"/>
+      <c r="BG112"/>
+      <c r="BH112"/>
+      <c r="BI112"/>
+      <c r="BJ112"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>402135.0</v>
+      </c>
+      <c r="B113" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="H113"/>
+      <c r="I113"/>
+      <c r="J113"/>
+      <c r="K113"/>
+      <c r="L113"/>
+      <c r="M113"/>
+      <c r="N113"/>
+      <c r="O113"/>
+      <c r="P113"/>
+      <c r="Q113"/>
+      <c r="R113"/>
+      <c r="S113"/>
+      <c r="T113"/>
+      <c r="U113"/>
+      <c r="V113"/>
+      <c r="W113"/>
+      <c r="X113"/>
+      <c r="Y113"/>
+      <c r="Z113"/>
+      <c r="AA113"/>
+      <c r="AB113" t="inlineStr">
         <is>
           <t>&lt;div class="border-b-2 border-sky-500 text-2xl "&gt; 
    &lt;i class="fa-solid fa-book "&gt;&lt;/i&gt; 
@@ -16825,115 +17092,17 @@
 &lt;/div&gt;</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
+      <c r="AC113" t="inlineStr">
         <is>
           <t>pb-2
 text-left text-pretty</t>
         </is>
       </c>
-      <c r="AD112" t="inlineStr">
+      <c r="AD113" t="inlineStr">
         <is>
           <t>Classes</t>
         </is>
       </c>
-      <c r="AE112"/>
-      <c r="AF112"/>
-      <c r="AG112"/>
-      <c r="AH112"/>
-      <c r="AI112"/>
-      <c r="AJ112"/>
-      <c r="AK112"/>
-      <c r="AL112"/>
-      <c r="AM112"/>
-      <c r="AN112"/>
-      <c r="AO112"/>
-      <c r="AP112"/>
-      <c r="AQ112"/>
-      <c r="AR112"/>
-      <c r="AS112"/>
-      <c r="AT112"/>
-      <c r="AU112"/>
-      <c r="AV112"/>
-      <c r="AW112"/>
-      <c r="AX112"/>
-      <c r="AY112"/>
-      <c r="AZ112"/>
-      <c r="BA112"/>
-      <c r="BB112"/>
-      <c r="BC112"/>
-      <c r="BD112"/>
-      <c r="BE112"/>
-      <c r="BF112"/>
-      <c r="BG112"/>
-      <c r="BH112"/>
-      <c r="BI112"/>
-      <c r="BJ112"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>402135.0</v>
-      </c>
-      <c r="B113" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="C113" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Hierarchy</t>
-        </is>
-      </c>
-      <c r="E113"/>
-      <c r="F113"/>
-      <c r="G113"/>
-      <c r="H113"/>
-      <c r="I113"/>
-      <c r="J113"/>
-      <c r="K113"/>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>Politica v2</t>
-        </is>
-      </c>
-      <c r="M113"/>
-      <c r="N113"/>
-      <c r="O113"/>
-      <c r="P113"/>
-      <c r="Q113"/>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>text-blue-500 font-light</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>text-stone-600</t>
-        </is>
-      </c>
-      <c r="V113"/>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>politic_filter</t>
-        </is>
-      </c>
-      <c r="X113"/>
-      <c r="Y113"/>
-      <c r="Z113"/>
-      <c r="AA113"/>
-      <c r="AB113"/>
-      <c r="AC113"/>
-      <c r="AD113"/>
       <c r="AE113"/>
       <c r="AF113"/>
       <c r="AG113"/>
@@ -16953,29 +17122,17 @@
       <c r="AU113"/>
       <c r="AV113"/>
       <c r="AW113"/>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>politic</t>
-        </is>
-      </c>
+      <c r="AX113"/>
       <c r="AY113"/>
       <c r="AZ113"/>
-      <c r="BA113" t="inlineStr">
-        <is>
-          <t>Política Mãe</t>
-        </is>
-      </c>
+      <c r="BA113"/>
       <c r="BB113"/>
       <c r="BC113"/>
       <c r="BD113"/>
       <c r="BE113"/>
       <c r="BF113"/>
       <c r="BG113"/>
-      <c r="BH113" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
+      <c r="BH113"/>
       <c r="BI113"/>
       <c r="BJ113"/>
     </row>
@@ -16984,14 +17141,14 @@
         <v>402135.0</v>
       </c>
       <c r="B114" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Hierarchy</t>
         </is>
       </c>
       <c r="E114"/>
@@ -17001,18 +17158,42 @@
       <c r="I114"/>
       <c r="J114"/>
       <c r="K114"/>
-      <c r="L114"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Politica v2</t>
+        </is>
+      </c>
       <c r="M114"/>
       <c r="N114"/>
       <c r="O114"/>
       <c r="P114"/>
       <c r="Q114"/>
-      <c r="R114"/>
-      <c r="S114"/>
-      <c r="T114"/>
-      <c r="U114"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>text-blue-500 font-light</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>text-stone-600</t>
+        </is>
+      </c>
       <c r="V114"/>
-      <c r="W114"/>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>politic_filter</t>
+        </is>
+      </c>
       <c r="X114"/>
       <c r="Y114"/>
       <c r="Z114"/>
@@ -17039,27 +17220,31 @@
       <c r="AU114"/>
       <c r="AV114"/>
       <c r="AW114"/>
-      <c r="AX114"/>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>politic</t>
+        </is>
+      </c>
       <c r="AY114"/>
       <c r="AZ114"/>
-      <c r="BA114"/>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>Política Mãe</t>
+        </is>
+      </c>
       <c r="BB114"/>
       <c r="BC114"/>
       <c r="BD114"/>
       <c r="BE114"/>
       <c r="BF114"/>
       <c r="BG114"/>
-      <c r="BH114"/>
-      <c r="BI114" t="inlineStr">
-        <is>
-          <t>absolute top-2 right-3</t>
-        </is>
-      </c>
-      <c r="BJ114" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="BH114" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="BI114"/>
+      <c r="BJ114"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -17069,11 +17254,11 @@
         <v>3.0</v>
       </c>
       <c r="C115" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E115"/>
@@ -17099,33 +17284,9 @@
       <c r="Y115"/>
       <c r="Z115"/>
       <c r="AA115"/>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>{{#if vars.politic}}
-   &lt;div class="border-b-2 border-sky-500 mb-2"&gt; 
-      &lt;a href="/recordm/#/instance/{{vars.politic.instanceId}}" class="text-2xl font-bold hover:text-cyan-700"&gt;
-         {{vars.politic.nome}} 
-         &lt;i class="fa-solid fa-pen-to-square text-sm"&gt; &lt;/i&gt;
-         &lt;span class="font-light pr-2 text-xs"&gt; ({{vars.politic.state}})  &lt;/span&gt; 
-      &lt;/a&gt;
-   &lt;/div&gt;
-{{else}}
-   &lt;div class="text-2xl absolute top-1/2 left-1/2 transform -translate-x-1/2 -translate-y-1/2"&gt; 
-      Select a policy to view it
-   &lt;/div&gt;
-{{/if}}</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>text-left text-pretty</t>
-        </is>
-      </c>
-      <c r="AD115" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB115"/>
+      <c r="AC115"/>
+      <c r="AD115"/>
       <c r="AE115"/>
       <c r="AF115"/>
       <c r="AG115"/>
@@ -17156,8 +17317,16 @@
       <c r="BF115"/>
       <c r="BG115"/>
       <c r="BH115"/>
-      <c r="BI115"/>
-      <c r="BJ115"/>
+      <c r="BI115" t="inlineStr">
+        <is>
+          <t>absolute top-2 right-3</t>
+        </is>
+      </c>
+      <c r="BJ115" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -17167,11 +17336,11 @@
         <v>3.0</v>
       </c>
       <c r="C116" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Markdown</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E116"/>
@@ -17197,26 +17366,124 @@
       <c r="Y116"/>
       <c r="Z116"/>
       <c r="AA116"/>
-      <c r="AB116"/>
-      <c r="AC116"/>
-      <c r="AD116"/>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>{{#if vars.politic}}
+   &lt;div class="border-b-2 border-sky-500 mb-2"&gt; 
+      &lt;a href="/recordm/#/instance/{{vars.politic.instanceId}}" class="text-2xl font-bold hover:text-cyan-700"&gt;
+         {{vars.politic.nome}} 
+         &lt;i class="fa-solid fa-pen-to-square text-sm"&gt; &lt;/i&gt;
+         &lt;span class="font-light pr-2 text-xs"&gt; ({{vars.politic.state}})  &lt;/span&gt; 
+      &lt;/a&gt;
+   &lt;/div&gt;
+{{else}}
+   &lt;div class="text-2xl absolute top-1/2 left-1/2 transform -translate-x-1/2 -translate-y-1/2"&gt; 
+      Select a policy to view it
+   &lt;/div&gt;
+{{/if}}</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>text-left text-pretty</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE116"/>
       <c r="AF116"/>
       <c r="AG116"/>
       <c r="AH116"/>
       <c r="AI116"/>
-      <c r="AJ116" t="inlineStr">
+      <c r="AJ116"/>
+      <c r="AK116"/>
+      <c r="AL116"/>
+      <c r="AM116"/>
+      <c r="AN116"/>
+      <c r="AO116"/>
+      <c r="AP116"/>
+      <c r="AQ116"/>
+      <c r="AR116"/>
+      <c r="AS116"/>
+      <c r="AT116"/>
+      <c r="AU116"/>
+      <c r="AV116"/>
+      <c r="AW116"/>
+      <c r="AX116"/>
+      <c r="AY116"/>
+      <c r="AZ116"/>
+      <c r="BA116"/>
+      <c r="BB116"/>
+      <c r="BC116"/>
+      <c r="BD116"/>
+      <c r="BE116"/>
+      <c r="BF116"/>
+      <c r="BG116"/>
+      <c r="BH116"/>
+      <c r="BI116"/>
+      <c r="BJ116"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>402135.0</v>
+      </c>
+      <c r="B117" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C117" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Markdown</t>
+        </is>
+      </c>
+      <c r="E117"/>
+      <c r="F117"/>
+      <c r="G117"/>
+      <c r="H117"/>
+      <c r="I117"/>
+      <c r="J117"/>
+      <c r="K117"/>
+      <c r="L117"/>
+      <c r="M117"/>
+      <c r="N117"/>
+      <c r="O117"/>
+      <c r="P117"/>
+      <c r="Q117"/>
+      <c r="R117"/>
+      <c r="S117"/>
+      <c r="T117"/>
+      <c r="U117"/>
+      <c r="V117"/>
+      <c r="W117"/>
+      <c r="X117"/>
+      <c r="Y117"/>
+      <c r="Z117"/>
+      <c r="AA117"/>
+      <c r="AB117"/>
+      <c r="AC117"/>
+      <c r="AD117"/>
+      <c r="AE117"/>
+      <c r="AF117"/>
+      <c r="AG117"/>
+      <c r="AH117"/>
+      <c r="AI117"/>
+      <c r="AJ117" t="inlineStr">
         <is>
           <t>overflow-y-auto text-justify text-gray-700</t>
         </is>
       </c>
-      <c r="AK116" t="inlineStr">
+      <c r="AK117" t="inlineStr">
         <is>
           <t>Classes</t>
         </is>
       </c>
-      <c r="AL116"/>
-      <c r="AM116" t="inlineStr">
+      <c r="AL117"/>
+      <c r="AM117" t="inlineStr">
         <is>
           <t>{{#if vars.politic.objetivo}}
    &lt;div class="text-xl font-bold border-b-2 border-sky-200"&gt; 
@@ -17268,92 +17535,6 @@
 {{/if}}</t>
         </is>
       </c>
-      <c r="AN116"/>
-      <c r="AO116"/>
-      <c r="AP116"/>
-      <c r="AQ116"/>
-      <c r="AR116"/>
-      <c r="AS116"/>
-      <c r="AT116"/>
-      <c r="AU116"/>
-      <c r="AV116"/>
-      <c r="AW116"/>
-      <c r="AX116"/>
-      <c r="AY116"/>
-      <c r="AZ116"/>
-      <c r="BA116"/>
-      <c r="BB116"/>
-      <c r="BC116"/>
-      <c r="BD116"/>
-      <c r="BE116"/>
-      <c r="BF116"/>
-      <c r="BG116"/>
-      <c r="BH116"/>
-      <c r="BI116"/>
-      <c r="BJ116"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>402135.0</v>
-      </c>
-      <c r="B117" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C117" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="E117"/>
-      <c r="F117"/>
-      <c r="G117"/>
-      <c r="H117"/>
-      <c r="I117"/>
-      <c r="J117"/>
-      <c r="K117"/>
-      <c r="L117"/>
-      <c r="M117"/>
-      <c r="N117"/>
-      <c r="O117"/>
-      <c r="P117"/>
-      <c r="Q117"/>
-      <c r="R117"/>
-      <c r="S117"/>
-      <c r="T117"/>
-      <c r="U117"/>
-      <c r="V117"/>
-      <c r="W117"/>
-      <c r="X117"/>
-      <c r="Y117"/>
-      <c r="Z117"/>
-      <c r="AA117"/>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>Selected Policy's Controls:</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>text-center font-bold pb-1 mb-1 text-xl border-b-2 border-sky-500</t>
-        </is>
-      </c>
-      <c r="AD117" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="AE117"/>
-      <c r="AF117"/>
-      <c r="AG117"/>
-      <c r="AH117"/>
-      <c r="AI117"/>
-      <c r="AJ117"/>
-      <c r="AK117"/>
-      <c r="AL117"/>
-      <c r="AM117"/>
       <c r="AN117"/>
       <c r="AO117"/>
       <c r="AP117"/>
@@ -17386,11 +17567,11 @@
         <v>4.0</v>
       </c>
       <c r="C118" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E118"/>
@@ -17416,26 +17597,26 @@
       <c r="Y118"/>
       <c r="Z118"/>
       <c r="AA118"/>
-      <c r="AB118"/>
-      <c r="AC118"/>
-      <c r="AD118"/>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>Selected Policy's Controls:</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>text-center font-bold pb-1 mb-1 text-xl border-b-2 border-sky-500</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE118"/>
       <c r="AF118"/>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>InputVar, ShowViews</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>{{controls_query}}</t>
-        </is>
-      </c>
+      <c r="AG118"/>
+      <c r="AH118"/>
+      <c r="AI118"/>
       <c r="AJ118"/>
       <c r="AK118"/>
       <c r="AL118"/>
@@ -17466,17 +17647,17 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>402134.0</v>
+        <v>402135.0</v>
       </c>
       <c r="B119" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>List</t>
         </is>
       </c>
       <c r="E119"/>
@@ -17507,9 +17688,21 @@
       <c r="AD119"/>
       <c r="AE119"/>
       <c r="AF119"/>
-      <c r="AG119"/>
-      <c r="AH119"/>
-      <c r="AI119"/>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>InputVar, ShowViews</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>{{controls_query}}</t>
+        </is>
+      </c>
       <c r="AJ119"/>
       <c r="AK119"/>
       <c r="AL119"/>
@@ -17535,30 +17728,22 @@
       <c r="BF119"/>
       <c r="BG119"/>
       <c r="BH119"/>
-      <c r="BI119" t="inlineStr">
-        <is>
-          <t>w-6/12 table-auto</t>
-        </is>
-      </c>
-      <c r="BJ119" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="BI119"/>
+      <c r="BJ119"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
         <v>402134.0</v>
       </c>
       <c r="B120" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C120" t="n">
         <v>0.0</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E120"/>
@@ -17573,11 +17758,7 @@
       <c r="N120"/>
       <c r="O120"/>
       <c r="P120"/>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
+      <c r="Q120"/>
       <c r="R120"/>
       <c r="S120"/>
       <c r="T120"/>
@@ -17609,42 +17790,42 @@
       <c r="AT120"/>
       <c r="AU120"/>
       <c r="AV120"/>
-      <c r="AW120" t="inlineStr">
-        <is>
-          <t>politic_filter</t>
-        </is>
-      </c>
+      <c r="AW120"/>
       <c r="AX120"/>
       <c r="AY120"/>
       <c r="AZ120"/>
       <c r="BA120"/>
-      <c r="BB120" t="inlineStr">
-        <is>
-          <t>Search Policies...</t>
-        </is>
-      </c>
+      <c r="BB120"/>
       <c r="BC120"/>
       <c r="BD120"/>
       <c r="BE120"/>
       <c r="BF120"/>
       <c r="BG120"/>
       <c r="BH120"/>
-      <c r="BI120"/>
-      <c r="BJ120"/>
+      <c r="BI120" t="inlineStr">
+        <is>
+          <t>w-6/12 table-auto</t>
+        </is>
+      </c>
+      <c r="BJ120" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
         <v>402134.0</v>
       </c>
       <c r="B121" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C121" t="n">
         <v>0.0</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="E121"/>
@@ -17659,7 +17840,11 @@
       <c r="N121"/>
       <c r="O121"/>
       <c r="P121"/>
-      <c r="Q121"/>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
       <c r="R121"/>
       <c r="S121"/>
       <c r="T121"/>
@@ -17691,42 +17876,42 @@
       <c r="AT121"/>
       <c r="AU121"/>
       <c r="AV121"/>
-      <c r="AW121"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>politic_filter</t>
+        </is>
+      </c>
       <c r="AX121"/>
       <c r="AY121"/>
       <c r="AZ121"/>
       <c r="BA121"/>
-      <c r="BB121"/>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>Search Policies...</t>
+        </is>
+      </c>
       <c r="BC121"/>
       <c r="BD121"/>
       <c r="BE121"/>
       <c r="BF121"/>
       <c r="BG121"/>
       <c r="BH121"/>
-      <c r="BI121" t="inlineStr">
-        <is>
-          <t>w-full table-auto rounded-md</t>
-        </is>
-      </c>
-      <c r="BJ121" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="BI121"/>
+      <c r="BJ121"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
         <v>402134.0</v>
       </c>
       <c r="B122" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C122" t="n">
         <v>0.0</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Hierarchy</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E122"/>
@@ -17736,43 +17921,19 @@
       <c r="I122"/>
       <c r="J122"/>
       <c r="K122"/>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>Politica v2</t>
-        </is>
-      </c>
+      <c r="L122"/>
       <c r="M122"/>
       <c r="N122"/>
       <c r="O122"/>
       <c r="P122"/>
       <c r="Q122"/>
       <c r="R122"/>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>text-blue-500 font-light</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>text-stone-600</t>
-        </is>
-      </c>
+      <c r="S122"/>
+      <c r="T122"/>
+      <c r="U122"/>
       <c r="V122"/>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>politic_filter</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
+      <c r="W122"/>
+      <c r="X122"/>
       <c r="Y122"/>
       <c r="Z122"/>
       <c r="AA122"/>
@@ -17798,45 +17959,41 @@
       <c r="AU122"/>
       <c r="AV122"/>
       <c r="AW122"/>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>politic</t>
-        </is>
-      </c>
+      <c r="AX122"/>
       <c r="AY122"/>
       <c r="AZ122"/>
-      <c r="BA122" t="inlineStr">
-        <is>
-          <t>Política Mãe</t>
-        </is>
-      </c>
+      <c r="BA122"/>
       <c r="BB122"/>
       <c r="BC122"/>
       <c r="BD122"/>
       <c r="BE122"/>
       <c r="BF122"/>
       <c r="BG122"/>
-      <c r="BH122" t="inlineStr">
-        <is>
-          <t>Nome</t>
-        </is>
-      </c>
-      <c r="BI122"/>
-      <c r="BJ122"/>
+      <c r="BH122"/>
+      <c r="BI122" t="inlineStr">
+        <is>
+          <t>w-full table-auto rounded-md</t>
+        </is>
+      </c>
+      <c r="BJ122" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
         <v>402134.0</v>
       </c>
       <c r="B123" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C123" t="n">
         <v>0.0</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Hierarchy</t>
         </is>
       </c>
       <c r="E123"/>
@@ -17846,25 +18003,45 @@
       <c r="I123"/>
       <c r="J123"/>
       <c r="K123"/>
-      <c r="L123"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Politica v2</t>
+        </is>
+      </c>
       <c r="M123"/>
       <c r="N123"/>
       <c r="O123"/>
       <c r="P123"/>
       <c r="Q123"/>
       <c r="R123"/>
-      <c r="S123"/>
-      <c r="T123"/>
-      <c r="U123"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>text-blue-500 font-light</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>text-stone-600</t>
+        </is>
+      </c>
       <c r="V123"/>
-      <c r="W123"/>
-      <c r="X123"/>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>politic_filter</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="Y123"/>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>InputVar</t>
-        </is>
-      </c>
+      <c r="Z123"/>
       <c r="AA123"/>
       <c r="AB123"/>
       <c r="AC123"/>
@@ -17888,37 +18065,45 @@
       <c r="AU123"/>
       <c r="AV123"/>
       <c r="AW123"/>
-      <c r="AX123"/>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>politic</t>
+        </is>
+      </c>
       <c r="AY123"/>
       <c r="AZ123"/>
-      <c r="BA123"/>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Política Mãe</t>
+        </is>
+      </c>
       <c r="BB123"/>
       <c r="BC123"/>
       <c r="BD123"/>
-      <c r="BE123" t="inlineStr">
-        <is>
-          <t>/kibana/s/governance/app/dashboards#/view/fde08c10-f814-11ee-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
-        </is>
-      </c>
+      <c r="BE123"/>
       <c r="BF123"/>
       <c r="BG123"/>
-      <c r="BH123"/>
+      <c r="BH123" t="inlineStr">
+        <is>
+          <t>Nome</t>
+        </is>
+      </c>
       <c r="BI123"/>
       <c r="BJ123"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>402133.0</v>
+        <v>402134.0</v>
       </c>
       <c r="B124" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="C124" t="n">
         <v>0.0</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="E124"/>
@@ -17942,23 +18127,15 @@
       <c r="W124"/>
       <c r="X124"/>
       <c r="Y124"/>
-      <c r="Z124"/>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>InputVar</t>
+        </is>
+      </c>
       <c r="AA124"/>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>Template Policy Search</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>text-center text-2xl text-black font-bold mb-2</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB124"/>
+      <c r="AC124"/>
+      <c r="AD124"/>
       <c r="AE124"/>
       <c r="AF124"/>
       <c r="AG124"/>
@@ -17985,7 +18162,11 @@
       <c r="BB124"/>
       <c r="BC124"/>
       <c r="BD124"/>
-      <c r="BE124"/>
+      <c r="BE124" t="inlineStr">
+        <is>
+          <t>/kibana/s/governance/app/dashboards#/view/fde08c10-f814-11ee-93c0-e701f9603028?embed=true&amp;_g=(filters%3A!()%2CrefreshInterval%3A(pause%3A!t%2Cvalue%3A0)%2Ctime%3A(from%3Anow-1y%2Fd%2Cto%3Anow))&amp;hide-filter-bar=true</t>
+        </is>
+      </c>
       <c r="BF124"/>
       <c r="BG124"/>
       <c r="BH124"/>
@@ -17994,17 +18175,17 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>402133.0</v>
+        <v>402132.0</v>
       </c>
       <c r="B125" t="n">
         <v>0.0</v>
       </c>
       <c r="C125" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E125"/>
@@ -18018,16 +18199,8 @@
       <c r="M125"/>
       <c r="N125"/>
       <c r="O125"/>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>mb-2 rounded-md px-2 w-4/5 border border-slate-400</t>
-        </is>
-      </c>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>Classes, Placeholder</t>
-        </is>
-      </c>
+      <c r="P125"/>
+      <c r="Q125"/>
       <c r="R125"/>
       <c r="S125"/>
       <c r="T125"/>
@@ -18038,9 +18211,21 @@
       <c r="Y125"/>
       <c r="Z125"/>
       <c r="AA125"/>
-      <c r="AB125"/>
-      <c r="AC125"/>
-      <c r="AD125"/>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>Your introduction contents:</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>text-center font-bold pb-2 text-2xl text-black border-b-2 border-slate-400</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE125"/>
       <c r="AF125"/>
       <c r="AG125"/>
@@ -18059,20 +18244,12 @@
       <c r="AT125"/>
       <c r="AU125"/>
       <c r="AV125"/>
-      <c r="AW125" t="inlineStr">
-        <is>
-          <t>politicaSearch</t>
-        </is>
-      </c>
+      <c r="AW125"/>
       <c r="AX125"/>
       <c r="AY125"/>
       <c r="AZ125"/>
       <c r="BA125"/>
-      <c r="BB125" t="inlineStr">
-        <is>
-          <t>Search Policies...</t>
-        </is>
-      </c>
+      <c r="BB125"/>
       <c r="BC125"/>
       <c r="BD125"/>
       <c r="BE125"/>
@@ -18084,17 +18261,17 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>402133.0</v>
+        <v>402132.0</v>
       </c>
       <c r="B126" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C126" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E126"/>
@@ -18103,11 +18280,7 @@
       <c r="H126"/>
       <c r="I126"/>
       <c r="J126"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>PoliticaDash</t>
-        </is>
-      </c>
+      <c r="K126"/>
       <c r="L126"/>
       <c r="M126"/>
       <c r="N126"/>
@@ -18124,26 +18297,30 @@
       <c r="Y126"/>
       <c r="Z126"/>
       <c r="AA126"/>
-      <c r="AB126"/>
-      <c r="AC126"/>
-      <c r="AD126"/>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>{{#if (eq ../user.username 'rvalverde')}}
+&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
+{{else}}
+{{título_conteúdo}}
+{{/if}}</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>text-black text-2xl font-bold flex-none</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE126"/>
       <c r="AF126"/>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>InputVar, SetDefaultView</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>Politica v2</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>template:"Yes" {{vars.politicaSearch}} {{#each my_politics.value}} {{#if política_template}}  -id:”{{política_template}}” {{/if}} {{/each}}</t>
-        </is>
-      </c>
+      <c r="AG126"/>
+      <c r="AH126"/>
+      <c r="AI126"/>
       <c r="AJ126"/>
       <c r="AK126"/>
       <c r="AL126"/>
@@ -18174,13 +18351,13 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>402133.0</v>
+        <v>402132.0</v>
       </c>
       <c r="B127" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C127" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -18212,20 +18389,19 @@
       <c r="AA127"/>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>&lt;div class="flex flex-row"&gt;
-{{#if my_politics.value}}
-&lt;div&gt;
-&lt;a href="/recordm/index.html#/cob.custom-resource/1969/dash" onclick="" class="text-green-700 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-file-lines fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;View my Politics&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
-&lt;/div&gt;
-{{/if}}
-&lt;div&gt;
-&lt;a href="/recordm/index.html#/instance/create/38" onclick="" class="text-white bg-green-700 hover:bg-green-800 focus:outline-none focus:ring-4 focus:ring-green-300 font-medium rounded-full text-sm px-5 py-2.5 text-center me-2 mb-2 dark:bg-green-600 dark:hover:bg-green-700 dark:focus:ring-green-800 cursor-pointer"&gt;&lt;span&gt;&lt;i class="fa-file-lines fa-solid" style="margin-right: 4px;"&gt;&lt;/i&gt;&lt;span&gt;Create Policy&lt;/span&gt;&lt;/span&gt;&lt;!----&gt;&lt;/a&gt;
-&lt;/div&gt;
-&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="AC127"/>
-      <c r="AD127"/>
+          <t>{{resumo_conteúdo}}</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>text-left pb-2 flex-grow pt-2</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE127"/>
       <c r="AF127"/>
       <c r="AG127"/>
@@ -18264,14 +18440,14 @@
         <v>402132.0</v>
       </c>
       <c r="B128" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>ModalActivator</t>
         </is>
       </c>
       <c r="E128"/>
@@ -18297,21 +18473,9 @@
       <c r="Y128"/>
       <c r="Z128"/>
       <c r="AA128"/>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>Your introduction contents:</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>text-center font-bold pb-2 text-2xl text-black border-b-2 border-slate-400</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB128"/>
+      <c r="AC128"/>
+      <c r="AD128"/>
       <c r="AE128"/>
       <c r="AF128"/>
       <c r="AG128"/>
@@ -18324,10 +18488,26 @@
       <c r="AN128"/>
       <c r="AO128"/>
       <c r="AP128"/>
-      <c r="AQ128"/>
-      <c r="AR128"/>
-      <c r="AS128"/>
-      <c r="AT128"/>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>cursor-pointer text-sm flex-none</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr">
+        <is>
+          <t>{{id}}</t>
+        </is>
+      </c>
       <c r="AU128"/>
       <c r="AV128"/>
       <c r="AW128"/>
@@ -18350,21 +18530,25 @@
         <v>402132.0</v>
       </c>
       <c r="B129" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="C129" t="n">
         <v>0.0</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Slides</t>
         </is>
       </c>
       <c r="E129"/>
       <c r="F129"/>
       <c r="G129"/>
       <c r="H129"/>
-      <c r="I129"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>{{markdown_conteúdo}}</t>
+        </is>
+      </c>
       <c r="J129"/>
       <c r="K129"/>
       <c r="L129"/>
@@ -18383,25 +18567,9 @@
       <c r="Y129"/>
       <c r="Z129"/>
       <c r="AA129"/>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>{{#if (eq ../user.username 'rvalverde')}}
-&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
-{{else}}
-{{título_conteúdo}}
-{{/if}}</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>text-black text-2xl font-bold flex-none</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB129"/>
+      <c r="AC129"/>
+      <c r="AD129"/>
       <c r="AE129"/>
       <c r="AF129"/>
       <c r="AG129"/>
@@ -18440,10 +18608,10 @@
         <v>402132.0</v>
       </c>
       <c r="B130" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C130" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -18475,12 +18643,16 @@
       <c r="AA130"/>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>{{resumo_conteúdo}}</t>
+          <t>{{#if (eq ../user.username 'rvalverde')}}
+&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
+{{else}}
+{{not_seen.value.0.título_conteúdo}}
+{{/if}}</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>text-left pb-2 flex-grow pt-2</t>
+          <t>text-black text-2xl font-bold flex-none</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -18526,14 +18698,14 @@
         <v>402132.0</v>
       </c>
       <c r="B131" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C131" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ModalActivator</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E131"/>
@@ -18559,9 +18731,21 @@
       <c r="Y131"/>
       <c r="Z131"/>
       <c r="AA131"/>
-      <c r="AB131"/>
-      <c r="AC131"/>
-      <c r="AD131"/>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>{{not_seen.value.0.resumo_conteúdo}}</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>text-left pb-2 flex-grow pt-2</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
       <c r="AE131"/>
       <c r="AF131"/>
       <c r="AG131"/>
@@ -18574,26 +18758,10 @@
       <c r="AN131"/>
       <c r="AO131"/>
       <c r="AP131"/>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>cursor-pointer text-sm flex-none</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
-        </is>
-      </c>
-      <c r="AT131" t="inlineStr">
-        <is>
-          <t>{{id}}</t>
-        </is>
-      </c>
+      <c r="AQ131"/>
+      <c r="AR131"/>
+      <c r="AS131"/>
+      <c r="AT131"/>
       <c r="AU131"/>
       <c r="AV131"/>
       <c r="AW131"/>
@@ -18616,25 +18784,21 @@
         <v>402132.0</v>
       </c>
       <c r="B132" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C132" t="n">
         <v>2.0</v>
       </c>
-      <c r="C132" t="n">
-        <v>0.0</v>
-      </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Slides</t>
+          <t>ModalActivator</t>
         </is>
       </c>
       <c r="E132"/>
       <c r="F132"/>
       <c r="G132"/>
       <c r="H132"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>{{markdown_conteúdo}}</t>
-        </is>
-      </c>
+      <c r="I132"/>
       <c r="J132"/>
       <c r="K132"/>
       <c r="L132"/>
@@ -18668,10 +18832,26 @@
       <c r="AN132"/>
       <c r="AO132"/>
       <c r="AP132"/>
-      <c r="AQ132"/>
-      <c r="AR132"/>
-      <c r="AS132"/>
-      <c r="AT132"/>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>cursor-pointer text-sm flex-none</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr">
+        <is>
+          <t>{{not_seen.value.0.id}}</t>
+        </is>
+      </c>
       <c r="AU132"/>
       <c r="AV132"/>
       <c r="AW132"/>
@@ -18694,21 +18874,29 @@
         <v>402132.0</v>
       </c>
       <c r="B133" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C133" t="n">
         <v>0.0</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Slides</t>
         </is>
       </c>
       <c r="E133"/>
       <c r="F133"/>
       <c r="G133"/>
-      <c r="H133"/>
-      <c r="I133"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>slides_feeditem_update</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>{{#if not_seen}}{{not_seen.value.0.markdown_conteúdo}}{{/if}}</t>
+        </is>
+      </c>
       <c r="J133"/>
       <c r="K133"/>
       <c r="L133"/>
@@ -18727,25 +18915,9 @@
       <c r="Y133"/>
       <c r="Z133"/>
       <c r="AA133"/>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>{{#if (eq ../user.username 'rvalverde')}}
-&lt;a class="cursor-pointer" href="#/recordm/index.html#/instance/{{instanceId}}"&gt;{{título_conteúdo}}&lt;/a&gt;
-{{else}}
-{{not_seen.value.0.título_conteúdo}}
-{{/if}}</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>text-black text-2xl font-bold flex-none</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
+      <c r="AB133"/>
+      <c r="AC133"/>
+      <c r="AD133"/>
       <c r="AE133"/>
       <c r="AF133"/>
       <c r="AG133"/>
@@ -18774,272 +18946,14 @@
       <c r="BD133"/>
       <c r="BE133"/>
       <c r="BF133"/>
-      <c r="BG133"/>
+      <c r="BG133" t="inlineStr">
+        <is>
+          <t>EndOfContentTrigger</t>
+        </is>
+      </c>
       <c r="BH133"/>
       <c r="BI133"/>
       <c r="BJ133"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>402132.0</v>
-      </c>
-      <c r="B134" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C134" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="E134"/>
-      <c r="F134"/>
-      <c r="G134"/>
-      <c r="H134"/>
-      <c r="I134"/>
-      <c r="J134"/>
-      <c r="K134"/>
-      <c r="L134"/>
-      <c r="M134"/>
-      <c r="N134"/>
-      <c r="O134"/>
-      <c r="P134"/>
-      <c r="Q134"/>
-      <c r="R134"/>
-      <c r="S134"/>
-      <c r="T134"/>
-      <c r="U134"/>
-      <c r="V134"/>
-      <c r="W134"/>
-      <c r="X134"/>
-      <c r="Y134"/>
-      <c r="Z134"/>
-      <c r="AA134"/>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>{{not_seen.value.0.resumo_conteúdo}}</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>text-left pb-2 flex-grow pt-2</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="AE134"/>
-      <c r="AF134"/>
-      <c r="AG134"/>
-      <c r="AH134"/>
-      <c r="AI134"/>
-      <c r="AJ134"/>
-      <c r="AK134"/>
-      <c r="AL134"/>
-      <c r="AM134"/>
-      <c r="AN134"/>
-      <c r="AO134"/>
-      <c r="AP134"/>
-      <c r="AQ134"/>
-      <c r="AR134"/>
-      <c r="AS134"/>
-      <c r="AT134"/>
-      <c r="AU134"/>
-      <c r="AV134"/>
-      <c r="AW134"/>
-      <c r="AX134"/>
-      <c r="AY134"/>
-      <c r="AZ134"/>
-      <c r="BA134"/>
-      <c r="BB134"/>
-      <c r="BC134"/>
-      <c r="BD134"/>
-      <c r="BE134"/>
-      <c r="BF134"/>
-      <c r="BG134"/>
-      <c r="BH134"/>
-      <c r="BI134"/>
-      <c r="BJ134"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>402132.0</v>
-      </c>
-      <c r="B135" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C135" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>ModalActivator</t>
-        </is>
-      </c>
-      <c r="E135"/>
-      <c r="F135"/>
-      <c r="G135"/>
-      <c r="H135"/>
-      <c r="I135"/>
-      <c r="J135"/>
-      <c r="K135"/>
-      <c r="L135"/>
-      <c r="M135"/>
-      <c r="N135"/>
-      <c r="O135"/>
-      <c r="P135"/>
-      <c r="Q135"/>
-      <c r="R135"/>
-      <c r="S135"/>
-      <c r="T135"/>
-      <c r="U135"/>
-      <c r="V135"/>
-      <c r="W135"/>
-      <c r="X135"/>
-      <c r="Y135"/>
-      <c r="Z135"/>
-      <c r="AA135"/>
-      <c r="AB135"/>
-      <c r="AC135"/>
-      <c r="AD135"/>
-      <c r="AE135"/>
-      <c r="AF135"/>
-      <c r="AG135"/>
-      <c r="AH135"/>
-      <c r="AI135"/>
-      <c r="AJ135"/>
-      <c r="AK135"/>
-      <c r="AL135"/>
-      <c r="AM135"/>
-      <c r="AN135"/>
-      <c r="AO135"/>
-      <c r="AP135"/>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>cursor-pointer text-sm flex-none</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>&lt;button class="bg-blue-800 hover:bg-blue-700 text-white font-bold py-2 px-4 rounded-full"&gt; View &lt;/button&gt;</t>
-        </is>
-      </c>
-      <c r="AT135" t="inlineStr">
-        <is>
-          <t>{{not_seen.value.0.id}}</t>
-        </is>
-      </c>
-      <c r="AU135"/>
-      <c r="AV135"/>
-      <c r="AW135"/>
-      <c r="AX135"/>
-      <c r="AY135"/>
-      <c r="AZ135"/>
-      <c r="BA135"/>
-      <c r="BB135"/>
-      <c r="BC135"/>
-      <c r="BD135"/>
-      <c r="BE135"/>
-      <c r="BF135"/>
-      <c r="BG135"/>
-      <c r="BH135"/>
-      <c r="BI135"/>
-      <c r="BJ135"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>402132.0</v>
-      </c>
-      <c r="B136" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C136" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Slides</t>
-        </is>
-      </c>
-      <c r="E136"/>
-      <c r="F136"/>
-      <c r="G136"/>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>slides_feeditem_update</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>{{#if not_seen}}{{not_seen.value.0.markdown_conteúdo}}{{/if}}</t>
-        </is>
-      </c>
-      <c r="J136"/>
-      <c r="K136"/>
-      <c r="L136"/>
-      <c r="M136"/>
-      <c r="N136"/>
-      <c r="O136"/>
-      <c r="P136"/>
-      <c r="Q136"/>
-      <c r="R136"/>
-      <c r="S136"/>
-      <c r="T136"/>
-      <c r="U136"/>
-      <c r="V136"/>
-      <c r="W136"/>
-      <c r="X136"/>
-      <c r="Y136"/>
-      <c r="Z136"/>
-      <c r="AA136"/>
-      <c r="AB136"/>
-      <c r="AC136"/>
-      <c r="AD136"/>
-      <c r="AE136"/>
-      <c r="AF136"/>
-      <c r="AG136"/>
-      <c r="AH136"/>
-      <c r="AI136"/>
-      <c r="AJ136"/>
-      <c r="AK136"/>
-      <c r="AL136"/>
-      <c r="AM136"/>
-      <c r="AN136"/>
-      <c r="AO136"/>
-      <c r="AP136"/>
-      <c r="AQ136"/>
-      <c r="AR136"/>
-      <c r="AS136"/>
-      <c r="AT136"/>
-      <c r="AU136"/>
-      <c r="AV136"/>
-      <c r="AW136"/>
-      <c r="AX136"/>
-      <c r="AY136"/>
-      <c r="AZ136"/>
-      <c r="BA136"/>
-      <c r="BB136"/>
-      <c r="BC136"/>
-      <c r="BD136"/>
-      <c r="BE136"/>
-      <c r="BF136"/>
-      <c r="BG136" t="inlineStr">
-        <is>
-          <t>EndOfContentTrigger</t>
-        </is>
-      </c>
-      <c r="BH136"/>
-      <c r="BI136"/>
-      <c r="BJ136"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -20302,7 +20216,7 @@
         <v>402146.0</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C50" t="n">
         <v>1.0</v>
@@ -20327,7 +20241,7 @@
         <v>402146.0</v>
       </c>
       <c r="B51" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C51" t="n">
         <v>1.0</v>
@@ -20352,7 +20266,7 @@
         <v>402146.0</v>
       </c>
       <c r="B52" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C52" t="n">
         <v>1.0</v>
@@ -20377,7 +20291,7 @@
         <v>402146.0</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C53" t="n">
         <v>1.0</v>
@@ -20402,7 +20316,7 @@
         <v>402146.0</v>
       </c>
       <c r="B54" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C54" t="n">
         <v>1.0</v>
@@ -20427,7 +20341,7 @@
         <v>402146.0</v>
       </c>
       <c r="B55" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C55" t="n">
         <v>1.0</v>
@@ -20452,7 +20366,7 @@
         <v>402146.0</v>
       </c>
       <c r="B56" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C56" t="n">
         <v>1.0</v>
@@ -20477,7 +20391,7 @@
         <v>402146.0</v>
       </c>
       <c r="B57" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C57" t="n">
         <v>1.0</v>
@@ -20502,7 +20416,7 @@
         <v>402146.0</v>
       </c>
       <c r="B58" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C58" t="n">
         <v>1.0</v>
@@ -20527,7 +20441,7 @@
         <v>402146.0</v>
       </c>
       <c r="B59" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C59" t="n">
         <v>1.0</v>
@@ -20552,7 +20466,7 @@
         <v>402146.0</v>
       </c>
       <c r="B60" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C60" t="n">
         <v>1.0</v>
@@ -20577,7 +20491,7 @@
         <v>402146.0</v>
       </c>
       <c r="B61" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C61" t="n">
         <v>1.0</v>
@@ -20602,7 +20516,7 @@
         <v>402146.0</v>
       </c>
       <c r="B62" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C62" t="n">
         <v>1.0</v>
@@ -20627,7 +20541,7 @@
         <v>402146.0</v>
       </c>
       <c r="B63" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C63" t="n">
         <v>1.0</v>
@@ -20652,7 +20566,7 @@
         <v>402146.0</v>
       </c>
       <c r="B64" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C64" t="n">
         <v>1.0</v>
@@ -20677,7 +20591,7 @@
         <v>402146.0</v>
       </c>
       <c r="B65" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C65" t="n">
         <v>1.0</v>
@@ -20702,7 +20616,7 @@
         <v>402146.0</v>
       </c>
       <c r="B66" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C66" t="n">
         <v>1.0</v>
@@ -20727,7 +20641,7 @@
         <v>402146.0</v>
       </c>
       <c r="B67" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C67" t="n">
         <v>1.0</v>
@@ -20752,7 +20666,7 @@
         <v>402146.0</v>
       </c>
       <c r="B68" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C68" t="n">
         <v>1.0</v>
@@ -20777,7 +20691,7 @@
         <v>402146.0</v>
       </c>
       <c r="B69" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C69" t="n">
         <v>1.0</v>
@@ -20802,7 +20716,7 @@
         <v>402146.0</v>
       </c>
       <c r="B70" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C70" t="n">
         <v>3.0</v>
@@ -20827,7 +20741,7 @@
         <v>402146.0</v>
       </c>
       <c r="B71" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C71" t="n">
         <v>3.0</v>
@@ -20852,7 +20766,7 @@
         <v>402146.0</v>
       </c>
       <c r="B72" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C72" t="n">
         <v>3.0</v>
@@ -20877,7 +20791,7 @@
         <v>402146.0</v>
       </c>
       <c r="B73" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C73" t="n">
         <v>3.0</v>
@@ -20902,7 +20816,7 @@
         <v>402146.0</v>
       </c>
       <c r="B74" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C74" t="n">
         <v>1.0</v>
@@ -20927,7 +20841,7 @@
         <v>402146.0</v>
       </c>
       <c r="B75" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C75" t="n">
         <v>1.0</v>
@@ -20952,7 +20866,7 @@
         <v>402146.0</v>
       </c>
       <c r="B76" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C76" t="n">
         <v>1.0</v>
@@ -20977,7 +20891,7 @@
         <v>402146.0</v>
       </c>
       <c r="B77" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C77" t="n">
         <v>1.0</v>
@@ -21002,7 +20916,7 @@
         <v>402146.0</v>
       </c>
       <c r="B78" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C78" t="n">
         <v>1.0</v>
@@ -21027,7 +20941,7 @@
         <v>402146.0</v>
       </c>
       <c r="B79" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C79" t="n">
         <v>1.0</v>
@@ -23416,12 +23330,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Risk Classifications</t>
+          <t>Risk Filter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-3 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-12 rounded-md</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -23439,12 +23353,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Risks Totals Origin</t>
+          <t>Risk Work Items</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-3 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-2 m-1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -23462,12 +23376,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Risk Totals Datas Revisão</t>
+          <t>Risk Classifications</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-3 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-3 rounded-md border border-gray-300 bg-white bg-opacity-70 p-2 m-1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -23485,12 +23399,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Risk State</t>
+          <t>Risks Totals Origin</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-3 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-3 rounded-md border border-gray-300 bg-white bg-opacity-70 p-2 m-1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -23508,12 +23422,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Risk Filter</t>
+          <t>Risk Totals Datas Revisão</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-3 rounded-md border border-gray-300 bg-white bg-opacity-70 p-2 m-1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -23531,12 +23445,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Risk State</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-3 rounded-md border border-gray-300 bg-white bg-opacity-70 p-2 m-1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -23547,19 +23461,19 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>402145.0</v>
+        <v>402146.0</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vuln Totals</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-2 m-1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -23573,11 +23487,11 @@
         <v>402145.0</v>
       </c>
       <c r="B25" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Vuln Totals</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -23593,14 +23507,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>402144.0</v>
+        <v>402145.0</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Incidents</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -23616,19 +23530,19 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>402143.0</v>
+        <v>402144.0</v>
       </c>
       <c r="B27" t="n">
         <v>0.0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Threat Types Totals</t>
+          <t>Incidents</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-6 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -23642,11 +23556,11 @@
         <v>402143.0</v>
       </c>
       <c r="B28" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Threat Origin Totals</t>
+          <t>Threat Types Totals</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -23665,16 +23579,16 @@
         <v>402143.0</v>
       </c>
       <c r="B29" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Threat Origin Totals</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-6 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -23688,11 +23602,11 @@
         <v>402143.0</v>
       </c>
       <c r="B30" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -23708,14 +23622,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>402142.0</v>
+        <v>402143.0</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Totals Findings Estado</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -23734,11 +23648,11 @@
         <v>402142.0</v>
       </c>
       <c r="B32" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Controls Search</t>
+          <t>Totals Findings Estado</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -23757,11 +23671,11 @@
         <v>402142.0</v>
       </c>
       <c r="B33" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Controls Search</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -23777,14 +23691,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>402141.0</v>
+        <v>402142.0</v>
       </c>
       <c r="B34" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Titulares</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -23800,19 +23714,19 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>402140.0</v>
+        <v>402141.0</v>
       </c>
       <c r="B35" t="n">
         <v>0.0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Activities</t>
+          <t>Titulares</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1 relative</t>
+          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -23826,40 +23740,40 @@
         <v>402140.0</v>
       </c>
       <c r="B36" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Processo Atividades</t>
-        </is>
-      </c>
-      <c r="D36"/>
+          <t>Activities</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1 relative</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IsModal</t>
+          <t>Classes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>402139.0</v>
+        <v>402140.0</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estatíticas dos Tipos de Conteúdos</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>col-span-12 md:col-span-6 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
-        </is>
-      </c>
+          <t>Processo Atividades</t>
+        </is>
+      </c>
+      <c r="D37"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Classes</t>
+          <t>IsModal</t>
         </is>
       </c>
     </row>
@@ -23868,11 +23782,11 @@
         <v>402139.0</v>
       </c>
       <c r="B38" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estatíticas dos Perfis</t>
+          <t>Estatíticas dos Tipos de Conteúdos</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -23891,16 +23805,16 @@
         <v>402139.0</v>
       </c>
       <c r="B39" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kibana</t>
+          <t>Estatíticas dos Perfis</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-6 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -23911,19 +23825,19 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>402138.0</v>
+        <v>402139.0</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TitleDesc</t>
+          <t>Kibana</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-12 rounded-md bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -23937,16 +23851,16 @@
         <v>402138.0</v>
       </c>
       <c r="B41" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{{#each seen_content.value}} SeenContentActivator</t>
+          <t>TitleDesc</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-4 rounded-md border border-blue-500 bg-slate-200 bg-opacity-70 p-4 m-1 content-center hover:bg-slate-300 flex flex-col</t>
+          <t>col-span-12 md:col-span-12 rounded-md bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -23960,21 +23874,21 @@
         <v>402138.0</v>
       </c>
       <c r="B42" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{{#each seen_content.value}}{{id}}</t>
+          <t>{{#each seen_content.value}} SeenContentActivator</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>w-[80%] overflow-y-hidden bg-white rounded-md border-1 border-black</t>
+          <t>col-span-12 md:col-span-4 rounded-md border border-blue-500 bg-slate-200 bg-opacity-70 p-4 m-1 content-center hover:bg-slate-300 flex flex-col</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Classes, IsModal</t>
+          <t>Classes</t>
         </is>
       </c>
     </row>
@@ -23983,21 +23897,21 @@
         <v>402138.0</v>
       </c>
       <c r="B43" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{{#if not_seen.value}}UnseenContentActivator</t>
+          <t>{{#each seen_content.value}}{{id}}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-4 rounded-md border border-green-500 bg-emerald-300 bg-opacity-70 p-4 m-1 content-center hover:bg-emerald-400 flex flex-col</t>
+          <t>w-[80%] overflow-y-hidden bg-white rounded-md border-1 border-black</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Classes</t>
+          <t>Classes, IsModal</t>
         </is>
       </c>
     </row>
@@ -24006,44 +23920,44 @@
         <v>402138.0</v>
       </c>
       <c r="B44" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{{not_seen.value.0.id}}</t>
+          <t>{{#if not_seen.value}}UnseenContentActivator</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>w-[80%] overflow-hidden bg-white rounded-md border-1 border-black</t>
+          <t>col-span-12 md:col-span-4 rounded-md border border-green-500 bg-emerald-300 bg-opacity-70 p-4 m-1 content-center hover:bg-emerald-400 flex flex-col</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Classes, IsModal</t>
+          <t>Classes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>402137.0</v>
+        <v>402138.0</v>
       </c>
       <c r="B45" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TitleDesc</t>
+          <t>{{not_seen.value.0.id}}</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-12 rounded-md bg-opacity-70 p-2 m-1</t>
+          <t>w-[80%] overflow-hidden bg-white rounded-md border-1 border-black</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Classes</t>
+          <t>Classes, IsModal</t>
         </is>
       </c>
     </row>
@@ -24052,16 +23966,16 @@
         <v>402137.0</v>
       </c>
       <c r="B46" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Empresa</t>
+          <t>TitleDesc</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-4 rounded-md border border-slate-400 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-12 rounded-md bg-opacity-70 p-2 m-1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -24075,16 +23989,16 @@
         <v>402137.0</v>
       </c>
       <c r="B47" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Empresa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-8 rounded-md border border-slate-400 bg-white bg-opacity-70 p-4 m-1 relative</t>
+          <t>col-span-12 md:col-span-4 rounded-md border border-slate-400 bg-white bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -24098,16 +24012,16 @@
         <v>402137.0</v>
       </c>
       <c r="B48" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{{#if (eq mycolab.value.0.state 'Modules Seen')}}</t>
+          <t>List</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-12 rounded-md border border-slate-400 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-8 rounded-md border border-slate-400 bg-white bg-opacity-70 p-4 m-1 relative</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -24121,40 +24035,40 @@
         <v>402137.0</v>
       </c>
       <c r="B49" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Processo de Introdução</t>
-        </is>
-      </c>
-      <c r="D49"/>
+          <t>{{#if (eq mycolab.value.0.state 'Modules Seen')}}</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>col-span-12 md:col-span-12 rounded-md border border-slate-400 bg-white bg-opacity-70 p-4 m-1</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IsModal</t>
+          <t>Classes</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>402136.0</v>
+        <v>402137.0</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TitleDesc</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>col-span-12 md:col-span-12 rounded-md bg-opacity-70 p-4 m-1</t>
-        </is>
-      </c>
+          <t>Processo de Introdução</t>
+        </is>
+      </c>
+      <c r="D50"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Classes</t>
+          <t>IsModal</t>
         </is>
       </c>
     </row>
@@ -24163,16 +24077,16 @@
         <v>402136.0</v>
       </c>
       <c r="B51" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{{#each seen_content.value}} SeenContentActivator</t>
+          <t>TitleDesc</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-4 rounded-md border border-blue-500 bg-slate-200 bg-opacity-70 p-4 m-1 content-center hover:bg-slate-300 flex flex-col</t>
+          <t>col-span-12 md:col-span-12 rounded-md bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -24186,21 +24100,21 @@
         <v>402136.0</v>
       </c>
       <c r="B52" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{{#each seen_content.value}}{{id}}</t>
+          <t>{{#each seen_content.value}} SeenContentActivator</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>w-[80%] overflow-y-hidden bg-white rounded-md border-1 border-black</t>
+          <t>col-span-12 md:col-span-4 rounded-md border border-blue-500 bg-slate-200 bg-opacity-70 p-4 m-1 content-center hover:bg-slate-300 flex flex-col</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Classes, IsModal</t>
+          <t>Classes</t>
         </is>
       </c>
     </row>
@@ -24209,21 +24123,21 @@
         <v>402136.0</v>
       </c>
       <c r="B53" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{{#if not_seen.value}}UnseenContentActivator</t>
+          <t>{{#each seen_content.value}}{{id}}</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-4 rounded-md border border-green-500 bg-emerald-300 bg-opacity-70 p-4 m-1 content-center hover:bg-emerald-400 flex flex-col</t>
+          <t>w-[80%] overflow-y-hidden bg-white rounded-md border-1 border-black</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Classes</t>
+          <t>Classes, IsModal</t>
         </is>
       </c>
     </row>
@@ -24232,44 +24146,44 @@
         <v>402136.0</v>
       </c>
       <c r="B54" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{{not_seen.value.0.id}}</t>
+          <t>{{#if not_seen.value}}UnseenContentActivator</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>w-[80%] overflow-hidden bg-white rounded-md border-1 border-black</t>
+          <t>col-span-12 md:col-span-4 rounded-md border border-green-500 bg-emerald-300 bg-opacity-70 p-4 m-1 content-center hover:bg-emerald-400 flex flex-col</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Classes, IsModal</t>
+          <t>Classes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>402135.0</v>
+        <v>402136.0</v>
       </c>
       <c r="B55" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HEADER</t>
+          <t>{{not_seen.value.0.id}}</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>col-span-4 col-start-4 col-end-8 md:col-span-12 p-4 m-1 flex justify-center</t>
+          <t>w-[80%] overflow-hidden bg-white rounded-md border-1 border-black</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Classes</t>
+          <t>Classes, IsModal</t>
         </is>
       </c>
     </row>
@@ -24278,16 +24192,16 @@
         <v>402135.0</v>
       </c>
       <c r="B56" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>HEADER</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>col-span-12 p-4 m-1</t>
+          <t>col-span-4 col-start-4 col-end-8 md:col-span-12 p-4 m-1 flex justify-center</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -24301,43 +24215,43 @@
         <v>402135.0</v>
       </c>
       <c r="B57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>col-span-12 p-4 m-1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>402135.0</v>
+      </c>
+      <c r="B58" t="n">
         <v>2.0</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Hierarchy of Policies</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>overflow-y-auto col-span-12 md:col-span-4 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1
 relative
 pb-12</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>402135.0</v>
-      </c>
-      <c r="B58" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Policy Viewer</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>col-span-12 md:col-span-8 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1 relative</t>
-        </is>
-      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>Classes</t>
@@ -24349,16 +24263,16 @@
         <v>402135.0</v>
       </c>
       <c r="B59" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{{#if vars.politic}} Policy's Control List</t>
+          <t>Policy Viewer</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-8 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1 relative</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -24369,19 +24283,19 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>402134.0</v>
+        <v>402135.0</v>
       </c>
       <c r="B60" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HEADER</t>
+          <t>{{#if vars.politic}} Policy's Control List</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>col-span-4 col-start-4 col-end-8 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1 flex justify-center</t>
+          <t>col-span-12 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -24395,16 +24309,16 @@
         <v>402134.0</v>
       </c>
       <c r="B61" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>HEADER</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-6 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-4 col-start-4 col-end-8 md:col-span-12 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1 flex justify-center</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -24418,11 +24332,11 @@
         <v>402134.0</v>
       </c>
       <c r="B62" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Selected Mat</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -24441,16 +24355,16 @@
         <v>402134.0</v>
       </c>
       <c r="B63" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hierarchy</t>
+          <t>Selected Mat</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-3 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-6 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -24464,16 +24378,16 @@
         <v>402134.0</v>
       </c>
       <c r="B64" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Maturidade Overview</t>
+          <t>Hierarchy</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-9 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-3 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -24484,19 +24398,19 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>402133.0</v>
+        <v>402134.0</v>
       </c>
       <c r="B65" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Template</t>
+          <t>Maturidade Overview</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>col-span-12 md:col-span-12 rounded-md border border-slate-400 bg-white bg-opacity-70 p-4 m-1</t>
+          <t>col-span-12 md:col-span-9 rounded-md border border-gray-300 bg-white bg-opacity-70 p-4 m-1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -24732,7 +24646,7 @@
         <v>402146.0</v>
       </c>
       <c r="B3" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="C3" t="n">
         <v>0.0</v>
@@ -24923,25 +24837,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>402133.0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>politica_search</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
